--- a/Scraped Tweets - Nigeria/Wizarab_scope_relevant_full.xlsx
+++ b/Scraped Tweets - Nigeria/Wizarab_scope_relevant_full.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="428">
   <si>
     <t>rank</t>
   </si>
@@ -82,6 +82,9 @@
     <t>He is married for almost 10 years and courted for almost 11 years prior, of which the relationship was celibate. The only time he enjoyed sex during his marriage was when the wife was pregnant because she thought it would aid delivery. He is sex starved. https://t.co/ve7YjZXauE</t>
   </si>
   <si>
+    <t>That is your father snd mother's business. They chose themselves. Your relationship with them is different from their spousal relationship. https://t.co/ZA6VLuiE7v</t>
+  </si>
+  <si>
     <t>A lady once told me she told me she opened her marriage because she had little to no interest in sex and it felt selfish and wicked to watch her man starve just because she didn't like sex. That might just be the solution to marriages where only one partner has interest in sex.</t>
   </si>
   <si>
@@ -91,6 +94,15 @@
     <t>His friend's wife has lost interest in sexual relations and the guy is very frustrated. https://t.co/3nde14W09z</t>
   </si>
   <si>
+    <t>It is the world we live in. The world is generally not safe for anybody. It is ruthless. Protect your love ones from male and female wolves. https://t.co/lr2N8OxUL1</t>
+  </si>
+  <si>
+    <t>Your fear is valid because of your past relationship. But I think you're centering the relationship around money. An investment you want to recoup and that is fine. You'll know about a person by how they treat you in their words, action &amp;amp; general mannerism and not just promises https://t.co/7g5DQTIxWv</t>
+  </si>
+  <si>
+    <t>Growing up with different relations is not an excuse to want to fuck your sister. I can think of a 100 things you can do with your sister now you are finally reconciled. Sex is not one of them. Don't rape that babe ooo How did sex even come to your mind? 🤦‍♂️ https://t.co/nkvmHUF3cc</t>
+  </si>
+  <si>
     <t>This is not a reason to get married. Don't marry somebody simply because they have a child for you when the relationship is toxic. This one has even given up on sex for marriage wey never start. https://t.co/q9F9NxskMe</t>
   </si>
   <si>
@@ -100,13 +112,37 @@
     <t>His anger is understandable. Your desire to remain a virgin till marriage is not more important than his desire for sexual intimacy. You're both making selfish decisions. Well, he is waiting with you. Live in the moment and stop worrying about tomorrow. I'm not clairvoyant https://t.co/JCLNaoYil1</t>
   </si>
   <si>
+    <t>Every whore has their favourite client. You are hers. You want to save her. Who told you she needs saving? Is your mother's prayers a joke to you? If you marry her, that is your personal problem. Just know that is your kids' mother. You accept the love you think you deserve. https://t.co/IG5HyGTaPG</t>
+  </si>
+  <si>
+    <t>If you're no more interested in the relationship, just end it. I don't take swears with the bible seriously. People do that everyday in court and lie. You accept the love you think you deserve https://t.co/IAtY7IuXe6</t>
+  </si>
+  <si>
+    <t>@Only1bigcee He needs sex not a family. It is not cheating if the partner is aware</t>
+  </si>
+  <si>
+    <t>To sleep with the wife of a man offering you shelter is an insult and gross disrespect. You should leave that house immediately. https://t.co/0UlnzvlNPz</t>
+  </si>
+  <si>
     <t>It is sad how many of you are starving sexually in committed relations. Guys, know this. Women love sex a lot and a woman that loves you would always want sexual relations with you. Women love to be desired and have their bodies cherished. If she is starving you, my brother RUN</t>
   </si>
   <si>
+    <t>What stupid force? I'm not interested in your conversation. Why should any sensible guy be interested in a lady twerking for the public on social media? There is someone for everybody. The men who have no problem with it can go ahead to date them. https://t.co/uMVPOhy87b</t>
+  </si>
+  <si>
+    <t>@YhungNathan "MY KING" Her posts were filled with family and lovey-dovey pictures hyping him. Meanwhile, she was dying in the marriage</t>
+  </si>
+  <si>
+    <t>He ended the relationship over lack of sexual consent https://t.co/n9QqvZJrWM</t>
+  </si>
+  <si>
     <t>Now this is trauma. Unknown to him, his Ex and his best friend were dating and she connived with the best friend to ruin him. She not only broke his heart. They wrecked him financially all because he trusted her. He has now moved from grace to grass. https://t.co/CR6A6YQ072</t>
   </si>
   <si>
-    <t>He ended the relationship over lack of sexual consent https://t.co/n9QqvZJrWM</t>
+    <t>You people that always get pained whenever a virgin speaks up, you need to tell us what your problem is because it can't be well with you. Everyday, you talk about sex and it is not a problem but you want to police virgins. It is nobody's fault you're not a virgin. Jealous cunt</t>
+  </si>
+  <si>
+    <t>She told me she wasn't cheating because she didn't need it. She just doesnt like or need sex and it made no sense for another person to starve because of her. Her only demand was that he doesn't share the details with her.</t>
   </si>
   <si>
     <t>I see why men don't take responses to tweets like this seriously. Only on Twitter nobody cooks for a man or do anything when they visit. You people tweet like nobody knows you. I didn't say "your man" because it might be side nigga or someone paying for sex you doing it for.</t>
@@ -115,42 +151,126 @@
     <t>I blame the man. He should be able to handle his affairs without this fuss.</t>
   </si>
   <si>
+    <t>This shouldnt be posted as an L. This was just gross irresponsibility and wickedness on the part of the guy. We shouldn't mock people for being kind and loving to their partners.</t>
+  </si>
+  <si>
+    <t>I hope you find the strength. Here is also praying you heal from the trauma 🙏🏾 https://t.co/pdofvn5hTy</t>
+  </si>
+  <si>
+    <t>The point of relationship is to know if someone is compatibility you or not. If they are not. You quit. You admit tou are tired. What do you think is the appropriate action? https://t.co/0GhB0p9X7d</t>
+  </si>
+  <si>
+    <t>Fact. Chasing is for the thrill. It has nothing to do with your value. Some men enjoy the thrill. Personally, I don't.</t>
+  </si>
+  <si>
     <t>If he doesn't initiate sex, he won't have sex with the wife. https://t.co/WSTcxv1CZl</t>
   </si>
   <si>
+    <t>You have to be fully in or fully out. Kill every dependency by blocking him after the break up or you fix whatever issues you have and continue the relationship This confusion is what lead to women ending their relationship and becoming side chics to their Ex. Piss in one place https://t.co/Is4TsBAnHc</t>
+  </si>
+  <si>
+    <t>Today go long ooo. Many people are starving and sexually frustrated in their relationship or marriage. Feel free to send a DM</t>
+  </si>
+  <si>
+    <t>You go knack abi you no go knack? Since you know he has a babe, why are you talking to him a lot? You want him to define what you have when you know he has a babe. What else is there to define? You are hoping he leaves his babe for you one day. Dey play https://t.co/M5VUdORRxp</t>
+  </si>
+  <si>
+    <t>It is what it is. But don't use your Ex to judge your babe. https://t.co/QEmN5v7AiN</t>
+  </si>
+  <si>
+    <t>@SoloJah1 @asaugoch This is not the point. Look at the last word in the tweet. "MY KING" Her posts were filled with family pictures hyping him</t>
+  </si>
+  <si>
+    <t>Una dey para ooo 😂😂😂 But the saddest thing I've heard is Nigerian men paying their babes to knack. There is no low we haven't sunk to in this country.</t>
+  </si>
+  <si>
     <t>End the relationship. That is manipulation and it is up to you to fall for the manipulation or not. Don't stay in a relationship because the other person is threatening to or attempting suicide. It is bullshit! It is an unhealthy obsession and very detrental to your well being. https://t.co/CTsRjdSPMW</t>
   </si>
   <si>
-    <t>I miss the fact you are cheating too. Well, good luck 🤷‍♂️</t>
+    <t>Life don better for you and you want to dump him because "we are not on the same level." He has done a lot but he should go and get his type because you want to shoot up. SMH You're not a good person. It is what it is sha. https://t.co/tSnnFKrbwb</t>
   </si>
   <si>
     <t>She dey use hmmmm collect boys salary. - Olamide son talk am</t>
   </si>
   <si>
+    <t>The pain is normal It will hurt for a while and then it will pass. It is the memories that hurt. Time brings healing. You're just 21. You'll be fine and you'll love again 🫂 https://t.co/ynYYgwvMU0</t>
+  </si>
+  <si>
+    <t>This clown that said he is wiser than his mother and more experienced than her, was looking up to Eniola Badmus and Seyi Law 😂😂 If Eniola Badmus is your role model and you have sense more than your mother, what Di we now think of your mother?</t>
+  </si>
+  <si>
+    <t>If you're very active on social media, then take advantage of social media. You don't need to step out to experience love. https://t.co/CMD8NR3seS</t>
+  </si>
+  <si>
+    <t>Guys, "choke me" no mean say make you strangle am abeg https://t.co/1xldPYBYAZ</t>
+  </si>
+  <si>
+    <t>Chatting, hanging out and hosting are some people's expertise. It comes naturally to them. You're not special. Because they do it right and ypu feel special, you think the stars have aligned but you don't really know them. You know the personality they put out publicly.</t>
+  </si>
+  <si>
+    <t>She just called him a mumu</t>
+  </si>
+  <si>
+    <t>@kenychordz You don't understand his tweet</t>
+  </si>
+  <si>
     <t>If you're a rapist, that is your personal problem.</t>
   </si>
   <si>
     <t>@mzibifaka He married her a virgin.</t>
   </si>
   <si>
+    <t>@Akuluouno1 He married her a virgin</t>
+  </si>
+  <si>
     <t>The conversation does not apply to you. You were a minor &amp;amp; he took advantage of you. It wouldn't have mattered if you liked him and wanted it or even asked for it. Consensual sex cannot happen between a minor and adult. You were raped and I'm sorry about that. I hope you heal🙏🏾 https://t.co/eIcQKGIz4h</t>
   </si>
   <si>
+    <t>That depends on your partner. Ask them https://t.co/GvhkH5Ywri</t>
+  </si>
+  <si>
     <t>@jhays7ven Even women beg for sex.</t>
   </si>
   <si>
     <t>You need to read this. This is one of the most annoying things I've read. But then, we accept the love we think we deserve. You men need to wake up https://t.co/RtewPOJbrp</t>
   </si>
   <si>
+    <t>@sanctemalum Sex is a very important factor</t>
+  </si>
+  <si>
+    <t>You people should advise him. https://t.co/vJnaD1IuiX</t>
+  </si>
+  <si>
+    <t>@ChineduNwota They agreed on CD. He too doesn't want STD from outside. Someone that married a virgin.</t>
+  </si>
+  <si>
+    <t>God help both of you https://t.co/T981lgZoti</t>
+  </si>
+  <si>
     <t>No it doesn't. Some first dates are preceded by days or weeks of conversation. Hence, depending on how the date goes, anything can happen. I personally dont recommend sex on first date because it clouds your reasoning. If you're sure you want to commit to the person then 🤷‍♂️ https://t.co/rD6v8rUguS</t>
   </si>
   <si>
     <t>MEN Lets go with this. How many consecutive times would your partner deny you sex because she is not in the mood before you stop initiating sex or blank her sexually?</t>
   </si>
   <si>
+    <t>Hypergamy. You're not her favourite option. Throw her away and stop giving her attention. BLOCK her https://t.co/gVijskvV3z</t>
+  </si>
+  <si>
+    <t>Baba say, take her life but leave my children out of it 😂😂</t>
+  </si>
+  <si>
+    <t>Why is the manipulation working? Nobody can manipulate you without your say so. You consented to the sex. What is her end game since you know it is manipulation https://t.co/s2Ws3YaEda</t>
+  </si>
+  <si>
     <t>Equality is a myth. They need to piss in one place so it can foam.</t>
   </si>
   <si>
+    <t>We need to be careful with the inclusion agenda. When people who can't accept rejection face rejection, they try to pin it on the fact they are black, coloured, female, transgender, gay, tribe or religion. How do we draw the line on people's entitlement to employer's own demand?</t>
+  </si>
+  <si>
+    <t>May the family find fortitude 🙏🏾</t>
+  </si>
+  <si>
     <t>LMAO...... The game is the game. Stop using sex as a power move. https://t.co/Dd3PEMufkg</t>
   </si>
   <si>
@@ -160,19 +280,82 @@
     <t>Question is, how is he treating currently? You'll know if someone really loves you and wants to commit to you or they are just happy you're funding them. Even in random conversations, you'll know. Please pay attention. https://t.co/fDftNhJ6UB</t>
   </si>
   <si>
-    <t>I see decent and dateable girls on Twitter everyday. Filter your TL https://t.co/z4sZAu0Sm4</t>
+    <t>@Tuwailuv @SonayanAjose No it isn't. He wants sex not a family. How many people have you pregnant educated or contracted STD from?</t>
+  </si>
+  <si>
+    <t>"A lot of them" are not your problem. Go for the one that fits into your life. https://t.co/RtdI7DWojd</t>
+  </si>
+  <si>
+    <t>We accept the love we think we deserve</t>
+  </si>
+  <si>
+    <t>Stop threatening people with their nude. You want to commit a crime over twitter bant?</t>
   </si>
   <si>
     <t>@Ol0ye Of course there is that. I was addressing the part of insecurity when there is none to be insecure about. I'm not going to call you confident and body positive if you're obese. I think they punish themselves a lot by striving for perfection that doesn't exist and comparison.</t>
   </si>
   <si>
+    <t>You make friends by being friendly. I didn't go out seeking friendships. They happened naturally. As for women, just walk up to them or send a DM and say what you want to say. If you're shy, it is okay. Tell her you're are shy and smile. She is human. Go with the flow. https://t.co/7aQVXcVml8</t>
+  </si>
+  <si>
+    <t>@BelMamacita They are not knacking enough and she is complaining. Lol</t>
+  </si>
+  <si>
+    <t>You're a place holder. Throw him away. Stop vouching for a person's love when they haven't shown you're the one they want in their life to the exclusion of all others. https://t.co/EVGVSxVPFX</t>
+  </si>
+  <si>
+    <t>America is not a country. How much is he earning that he would give her $4800 every month?</t>
+  </si>
+  <si>
     <t>Me leaving in day 3 days after putting in a good performance when she starts catching feelings and ask "so what are we?" https://t.co/tfeBndHZTa</t>
   </si>
   <si>
     <t>You're mad on several levels. There is absolutely nothing wrong with manipulation. Manipulation is not coercion. READ!!! You're a fucking adult. Your No should be your No. Begging for anything can be exhausting but does that make it robbery?</t>
   </si>
   <si>
-    <t>Lets discuss grace. This topic causes confusion among many because if we are saved by grace then what about condemnation for those who sin? Why do we repent if we are already saved? Endless questions What is grace for Christains? Back up your point with scripture.</t>
+    <t>@egoyibonwa19 People believe what they want to believe.</t>
+  </si>
+  <si>
+    <t>@Crechend0 Not really. But it does help them feel confident.</t>
+  </si>
+  <si>
+    <t>You have to take conscious step to quit gambling and focus on self development. You'll be fine. You are not too lost to recover. https://t.co/sq1Mg99c1Y</t>
+  </si>
+  <si>
+    <t>@Mrpossidez someone is offering you that luscious mammaries you're yearning for. I can't speak for him. You should enter his DM and find out. https://t.co/O5JuayYaHV</t>
+  </si>
+  <si>
+    <t>There is no fast way. It is not magic. Just accept they aren't for you and that there are many good fishes in the river. https://t.co/TjCRfRN3Hn</t>
+  </si>
+  <si>
+    <t>She has her reasons I guess https://t.co/svjgYGFrcx</t>
+  </si>
+  <si>
+    <t>Tell him to stop making promises and just do what he can. https://t.co/cx23f0gaqq</t>
+  </si>
+  <si>
+    <t>One day, you'll get what is coming for you. https://t.co/7y0IF85IiJ</t>
+  </si>
+  <si>
+    <t>Peter Obi won't fix the human damages of a people that we are. He will do the best he can at the top of the political spectrum for collective benefits. But the citizens will remain who they are irrespective of who is in power. We are innately corrupt.</t>
+  </si>
+  <si>
+    <t>What is Thaddeus Attah twitter handle? Maybe he can be invited to speak on space. You people are bullying him because he doesn't have a sort of appearance. At least, he is in Labour. He knows if he doesn't perform or he ports, he will be voted out. Stop the bullying.</t>
+  </si>
+  <si>
+    <t>@Toheeb2509 Looking at the industry, it is Eniola he is looking up to and you say he has sense</t>
+  </si>
+  <si>
+    <t>We all know what we are doing. She doesn't even believe herself.</t>
+  </si>
+  <si>
+    <t>Block her and never talk to her again. https://t.co/LEaKGSXtiY</t>
+  </si>
+  <si>
+    <t>Remove that jealousy from your neck.</t>
+  </si>
+  <si>
+    <t>@ZeekiHodl Na still why him no get sense. Him look everywhere, na Eniola him dey look up to</t>
   </si>
   <si>
     <t>rape, sexual violence and accountability</t>
@@ -184,18 +367,24 @@
     <t>feminism, misogyny and women's rights</t>
   </si>
   <si>
+    <t>fatherhood and raising sons and daughters</t>
+  </si>
+  <si>
+    <t>male victimhood and abuse of boys</t>
+  </si>
+  <si>
     <t>faith, partnership and trust in marriage</t>
   </si>
   <si>
     <t>polygamy and female scarcity narratives</t>
   </si>
   <si>
-    <t>male victimhood and abuse of boys</t>
-  </si>
-  <si>
     <t>dating standards and expectations between men and women</t>
   </si>
   <si>
+    <t>women's bodies, sexuality, and respectability</t>
+  </si>
+  <si>
     <t>views on what it means to be a man</t>
   </si>
   <si>
@@ -205,127 +394,313 @@
     <t>money, status and masculinity</t>
   </si>
   <si>
-    <t>women's bodies, sexuality, and respectability</t>
+    <t>advice to young men or young women</t>
+  </si>
+  <si>
+    <t>child support, divorce, and parenting responsibilities</t>
   </si>
   <si>
     <t>religion and gender expectations</t>
   </si>
   <si>
-    <t>Acknowledges rape and victim experience</t>
-  </si>
-  <si>
-    <t>Discusses cheating and marital deal breakers</t>
-  </si>
-  <si>
-    <t>Engages with patriarchy and gender equality.</t>
-  </si>
-  <si>
-    <t>Defines cheating in terms of consent</t>
-  </si>
-  <si>
-    <t>Explores infidelity and sexual deprivation</t>
-  </si>
-  <si>
-    <t>Discusses marriage and sexual starvation</t>
-  </si>
-  <si>
-    <t>Highlights sexual frustration in marriage</t>
-  </si>
-  <si>
-    <t>Details long-term celibate marriage and sexual issues</t>
-  </si>
-  <si>
-    <t>Explores alternative marriage solutions for sexual disinterest</t>
-  </si>
-  <si>
-    <t>Discusses trust and emotional connection in relationships</t>
-  </si>
-  <si>
-    <t>Frustration over lack of sexual relations</t>
-  </si>
-  <si>
-    <t>Discusses toxic relationships and marriage reasons</t>
-  </si>
-  <si>
-    <t>Engages with gender dynamics and sexual coercion.</t>
-  </si>
-  <si>
-    <t>Addresses sexual intimacy and virginity</t>
-  </si>
-  <si>
-    <t>Discusses female sexuality and desire</t>
-  </si>
-  <si>
-    <t>Highlights betrayal and financial impact in relationships</t>
-  </si>
-  <si>
-    <t>Discusses relationship and sexual consent issues</t>
-  </si>
-  <si>
-    <t>Discusses gender roles in relationships</t>
-  </si>
-  <si>
-    <t>Blames man for handling affairs poorly</t>
-  </si>
-  <si>
-    <t>Discusses sexual initiation dynamics in marriage</t>
-  </si>
-  <si>
-    <t>Discusses unhealthy relationship dynamics</t>
-  </si>
-  <si>
-    <t>Mentions infidelity and relationship dynamics</t>
-  </si>
-  <si>
-    <t>Engages with female agency and stereotypes</t>
-  </si>
-  <si>
-    <t>Engages with sexual violence and consent</t>
-  </si>
-  <si>
-    <t>Engages with marriage and virginity theme</t>
-  </si>
-  <si>
-    <t>Engages with consent and sexual violence</t>
-  </si>
-  <si>
-    <t>Comments on female agency in sexual contexts</t>
-  </si>
-  <si>
-    <t>Calls for men to wake up regarding love</t>
-  </si>
-  <si>
-    <t>Discusses dating norms and sexual morality.</t>
-  </si>
-  <si>
-    <t>Questions sexual initiation and denial in relationships</t>
-  </si>
-  <si>
-    <t>Discusses equality and gender dynamics.</t>
-  </si>
-  <si>
-    <t>Engages with sex as power dynamics</t>
-  </si>
-  <si>
-    <t>Discusses sexual interest and denial dynamics</t>
-  </si>
-  <si>
-    <t>Explores financial dynamics in relationships</t>
-  </si>
-  <si>
-    <t>Discusses dating and gender dynamics</t>
-  </si>
-  <si>
-    <t>Discusses body image and insecurity</t>
-  </si>
-  <si>
-    <t>Discusses dating dynamics and emotional expectations</t>
-  </si>
-  <si>
-    <t>Discusses manipulation and consent dynamics</t>
-  </si>
-  <si>
-    <t>Engages with faith and moral questions</t>
+    <t>Addresses rape and its impact on individuals</t>
+  </si>
+  <si>
+    <t>Discussion on cheating and marital deal breakers</t>
+  </si>
+  <si>
+    <t>Discusses gender dynamics and patriarchy.</t>
+  </si>
+  <si>
+    <t>Defines cheating in the context of consent</t>
+  </si>
+  <si>
+    <t>Explores infidelity due to sexual deprivation</t>
+  </si>
+  <si>
+    <t>Explores celibacy and sexual dissatisfaction in marriage</t>
+  </si>
+  <si>
+    <t>Sexual consent issues in marriage</t>
+  </si>
+  <si>
+    <t>Describes sexual starvation in long-term marriage</t>
+  </si>
+  <si>
+    <t>Family relationships vs. spousal relationships</t>
+  </si>
+  <si>
+    <t>Openness in marriage regarding sex</t>
+  </si>
+  <si>
+    <t>Discusses trust and emotional connections in relationships</t>
+  </si>
+  <si>
+    <t>Highlights frustration over lack of sexual relations</t>
+  </si>
+  <si>
+    <t>Mentions protecting loved ones from dangers</t>
+  </si>
+  <si>
+    <t>Discusses relationship dynamics and money</t>
+  </si>
+  <si>
+    <t>Discussion on consent and sexual morality.</t>
+  </si>
+  <si>
+    <t>Comments on marriage and toxic relationships</t>
+  </si>
+  <si>
+    <t>Discusses gender dynamics in sexual coercion</t>
+  </si>
+  <si>
+    <t>Explores virginity and sexual intimacy in relationships</t>
+  </si>
+  <si>
+    <t>Comments on relationships and personal choices</t>
+  </si>
+  <si>
+    <t>Ending relationships and self-worth</t>
+  </si>
+  <si>
+    <t>Sexual needs vs family dynamics</t>
+  </si>
+  <si>
+    <t>Infidelity and respect in relationships</t>
+  </si>
+  <si>
+    <t>Comments on sexual desire and relationship health</t>
+  </si>
+  <si>
+    <t>Views on female behavior and dating preferences.</t>
+  </si>
+  <si>
+    <t>Contrasting public image and private struggles</t>
+  </si>
+  <si>
+    <t>Ending relationship over consent</t>
+  </si>
+  <si>
+    <t>Discusses betrayal and financial ruin in relationships</t>
+  </si>
+  <si>
+    <t>Discussion on virginity and societal expectations.</t>
+  </si>
+  <si>
+    <t>Discusses female sexuality and relationship dynamics</t>
+  </si>
+  <si>
+    <t>Comments on gender roles and expectations</t>
+  </si>
+  <si>
+    <t>Blames man for relationship issues.</t>
+  </si>
+  <si>
+    <t>Critique of relationship dynamics and kindness.</t>
+  </si>
+  <si>
+    <t>Support for healing from trauma</t>
+  </si>
+  <si>
+    <t>Compatibility in relationships</t>
+  </si>
+  <si>
+    <t>Men's thrill in dating dynamics</t>
+  </si>
+  <si>
+    <t>Mentions sexual initiation in marriage</t>
+  </si>
+  <si>
+    <t>Dependency and relationship dynamics</t>
+  </si>
+  <si>
+    <t>Sexual frustration in relationships</t>
+  </si>
+  <si>
+    <t>Discussing relationships and infidelity</t>
+  </si>
+  <si>
+    <t>Judging partners based on past relationships</t>
+  </si>
+  <si>
+    <t>Insecurity and family dynamics</t>
+  </si>
+  <si>
+    <t>Comments on Nigerian men's behavior and relationships</t>
+  </si>
+  <si>
+    <t>Talks about unhealthy relationship dynamics</t>
+  </si>
+  <si>
+    <t>Commentary on relationship expectations and social status.</t>
+  </si>
+  <si>
+    <t>Implied commentary on female behavior</t>
+  </si>
+  <si>
+    <t>Healing from heartbreak and emotional expression</t>
+  </si>
+  <si>
+    <t>Comments on role models and maternal respect</t>
+  </si>
+  <si>
+    <t>Social media's role in modern love</t>
+  </si>
+  <si>
+    <t>Sexual consent and communication</t>
+  </si>
+  <si>
+    <t>Social dynamics and personal interactions</t>
+  </si>
+  <si>
+    <t>Indirectly touches on gender dynamics</t>
+  </si>
+  <si>
+    <t>Engagement on understanding gender roles</t>
+  </si>
+  <si>
+    <t>Addresses personal responsibility in sexual violence</t>
+  </si>
+  <si>
+    <t>References marriage and virginity</t>
+  </si>
+  <si>
+    <t>Discusses marriage and virginity</t>
+  </si>
+  <si>
+    <t>Discussion on consent and sexual violence</t>
+  </si>
+  <si>
+    <t>Advice on partner dynamics</t>
+  </si>
+  <si>
+    <t>Comments on women's behavior regarding sex</t>
+  </si>
+  <si>
+    <t>Men need to wake up in relationships</t>
+  </si>
+  <si>
+    <t>Importance of sex in relationships</t>
+  </si>
+  <si>
+    <t>Seeking advice on relationship issues</t>
+  </si>
+  <si>
+    <t>Marriage and virginity discussion</t>
+  </si>
+  <si>
+    <t>General advice on relationships</t>
+  </si>
+  <si>
+    <t>Discusses sex and reasoning in dating</t>
+  </si>
+  <si>
+    <t>Men's perspective on sexual denial</t>
+  </si>
+  <si>
+    <t>Discusses hypergamy and relationship dynamics</t>
+  </si>
+  <si>
+    <t>Touches on fatherhood and children's welfare</t>
+  </si>
+  <si>
+    <t>Manipulation and consent in relationships</t>
+  </si>
+  <si>
+    <t>Comments on gender equality myth</t>
+  </si>
+  <si>
+    <t>Inclusion agenda touches on gender and entitlement.</t>
+  </si>
+  <si>
+    <t>Relates to family and emotional support.</t>
+  </si>
+  <si>
+    <t>Sex as a power move discussion</t>
+  </si>
+  <si>
+    <t>Impact of repeated sexual denial</t>
+  </si>
+  <si>
+    <t>Highlights commitment and financial dynamics in relationships</t>
+  </si>
+  <si>
+    <t>Discusses sexual desires versus family planning</t>
+  </si>
+  <si>
+    <t>Advice on choosing compatible partners</t>
+  </si>
+  <si>
+    <t>Self-worth in love</t>
+  </si>
+  <si>
+    <t>Addresses threats related to consent</t>
+  </si>
+  <si>
+    <t>Body image and self-perception discussion</t>
+  </si>
+  <si>
+    <t>Mentions approaching women and social interactions</t>
+  </si>
+  <si>
+    <t>Comments on sexual activity and relationship complaints</t>
+  </si>
+  <si>
+    <t>Advice on relationship worth and value</t>
+  </si>
+  <si>
+    <t>Financial dynamics in relationships</t>
+  </si>
+  <si>
+    <t>Discusses relationship dynamics and feelings.</t>
+  </si>
+  <si>
+    <t>Explores manipulation and consent in adult relationships</t>
+  </si>
+  <si>
+    <t>Beliefs about relationships and social dynamics</t>
+  </si>
+  <si>
+    <t>Discusses confidence in relation to partners</t>
+  </si>
+  <si>
+    <t>Self-development advice for men</t>
+  </si>
+  <si>
+    <t>Implied sexual dynamics and behavior</t>
+  </si>
+  <si>
+    <t>Discusses dating and relationship perspectives</t>
+  </si>
+  <si>
+    <t>Implied reasons for female behavior</t>
+  </si>
+  <si>
+    <t>Implied relationship dynamics in promises</t>
+  </si>
+  <si>
+    <t>Implied consequences in relationships</t>
+  </si>
+  <si>
+    <t>Discusses societal behavior and corruption.</t>
+  </si>
+  <si>
+    <t>Addresses bullying and appearance in politics</t>
+  </si>
+  <si>
+    <t>Comments on role models and gender expectations</t>
+  </si>
+  <si>
+    <t>Indirectly touches on gender dynamics.</t>
+  </si>
+  <si>
+    <t>Advice on ending toxic relationships</t>
+  </si>
+  <si>
+    <t>Jealousy and relationships dynamics discussed.</t>
+  </si>
+  <si>
+    <t>Comments on male identity and perception</t>
   </si>
   <si>
     <t>2023-03-31 13:06:48+00:00</t>
@@ -352,6 +727,9 @@
     <t>2023-04-30 20:41:55+00:00</t>
   </si>
   <si>
+    <t>2023-05-31 10:58:21+00:00</t>
+  </si>
+  <si>
     <t>2023-04-30 09:47:59+00:00</t>
   </si>
   <si>
@@ -361,6 +739,15 @@
     <t>2023-04-30 19:39:22+00:00</t>
   </si>
   <si>
+    <t>2023-03-31 12:23:21+00:00</t>
+  </si>
+  <si>
+    <t>2023-03-31 12:33:26+00:00</t>
+  </si>
+  <si>
+    <t>2023-05-31 12:16:49+00:00</t>
+  </si>
+  <si>
     <t>2023-04-30 09:39:19+00:00</t>
   </si>
   <si>
@@ -370,13 +757,34 @@
     <t>2023-03-31 12:59:08+00:00</t>
   </si>
   <si>
+    <t>2023-05-31 23:39:42+00:00</t>
+  </si>
+  <si>
+    <t>2023-05-31 10:19:58+00:00</t>
+  </si>
+  <si>
+    <t>2023-04-30 09:57:39+00:00</t>
+  </si>
+  <si>
+    <t>2023-05-30 22:59:00+00:00</t>
+  </si>
+  <si>
     <t>2023-04-30 21:50:04+00:00</t>
   </si>
   <si>
+    <t>2023-05-31 12:07:18+00:00</t>
+  </si>
+  <si>
+    <t>2023-04-30 09:26:21+00:00</t>
+  </si>
+  <si>
+    <t>2023-04-30 10:54:12+00:00</t>
+  </si>
+  <si>
     <t>2023-04-30 20:53:39+00:00</t>
   </si>
   <si>
-    <t>2023-04-30 10:54:12+00:00</t>
+    <t>2023-05-31 21:38:37+00:00</t>
   </si>
   <si>
     <t>2023-04-30 11:13:27+00:00</t>
@@ -385,42 +793,126 @@
     <t>2023-01-29 16:17:57+00:00</t>
   </si>
   <si>
+    <t>2023-05-31 11:44:56+00:00</t>
+  </si>
+  <si>
+    <t>2023-03-31 19:52:10+00:00</t>
+  </si>
+  <si>
+    <t>2023-05-31 10:41:21+00:00</t>
+  </si>
+  <si>
+    <t>2023-05-31 07:59:12+00:00</t>
+  </si>
+  <si>
     <t>2023-04-30 17:42:23+00:00</t>
   </si>
   <si>
+    <t>2023-05-31 11:06:58+00:00</t>
+  </si>
+  <si>
+    <t>2023-04-30 09:33:06+00:00</t>
+  </si>
+  <si>
+    <t>2023-05-31 11:01:22+00:00</t>
+  </si>
+  <si>
+    <t>2023-05-31 11:31:27+00:00</t>
+  </si>
+  <si>
+    <t>2023-04-30 09:24:26+00:00</t>
+  </si>
+  <si>
+    <t>2023-04-30 09:06:59+00:00</t>
+  </si>
+  <si>
     <t>2023-03-31 12:36:06+00:00</t>
   </si>
   <si>
-    <t>2023-03-31 20:08:01+00:00</t>
+    <t>2023-05-31 12:03:08+00:00</t>
   </si>
   <si>
     <t>2023-01-29 21:52:38+00:00</t>
   </si>
   <si>
+    <t>2023-05-30 22:05:48+00:00</t>
+  </si>
+  <si>
+    <t>2023-02-28 09:13:49+00:00</t>
+  </si>
+  <si>
+    <t>2023-05-30 22:21:29+00:00</t>
+  </si>
+  <si>
+    <t>2023-05-31 10:03:36+00:00</t>
+  </si>
+  <si>
+    <t>2023-06-30 18:14:00+00:00</t>
+  </si>
+  <si>
+    <t>2023-02-28 21:33:50+00:00</t>
+  </si>
+  <si>
+    <t>2023-02-28 10:24:17+00:00</t>
+  </si>
+  <si>
     <t>2023-03-31 14:30:25+00:00</t>
   </si>
   <si>
     <t>2023-04-30 12:35:34+00:00</t>
   </si>
   <si>
+    <t>2023-04-30 12:35:03+00:00</t>
+  </si>
+  <si>
     <t>2023-03-31 19:49:39+00:00</t>
   </si>
   <si>
+    <t>2023-05-31 23:44:05+00:00</t>
+  </si>
+  <si>
     <t>2023-03-31 11:14:35+00:00</t>
   </si>
   <si>
     <t>2023-04-30 11:35:38+00:00</t>
   </si>
   <si>
+    <t>2023-04-30 09:58:06+00:00</t>
+  </si>
+  <si>
+    <t>2023-05-31 23:00:12+00:00</t>
+  </si>
+  <si>
+    <t>2023-04-30 09:59:46+00:00</t>
+  </si>
+  <si>
+    <t>2023-05-31 22:58:41+00:00</t>
+  </si>
+  <si>
     <t>2023-03-31 13:53:32+00:00</t>
   </si>
   <si>
     <t>2023-04-30 08:55:27+00:00</t>
   </si>
   <si>
+    <t>2023-05-31 23:25:18+00:00</t>
+  </si>
+  <si>
+    <t>2023-02-27 10:49:33+00:00</t>
+  </si>
+  <si>
+    <t>2023-05-31 10:05:25+00:00</t>
+  </si>
+  <si>
     <t>2023-01-31 09:49:56+00:00</t>
   </si>
   <si>
+    <t>2023-05-31 21:10:30+00:00</t>
+  </si>
+  <si>
+    <t>2023-01-30 19:56:31+00:00</t>
+  </si>
+  <si>
     <t>2023-04-30 09:52:21+00:00</t>
   </si>
   <si>
@@ -430,19 +922,82 @@
     <t>2023-03-31 12:33:34+00:00</t>
   </si>
   <si>
-    <t>2023-03-31 20:02:10+00:00</t>
+    <t>2023-04-30 19:33:26+00:00</t>
+  </si>
+  <si>
+    <t>2023-05-31 22:34:24+00:00</t>
+  </si>
+  <si>
+    <t>2023-05-31 07:52:42+00:00</t>
+  </si>
+  <si>
+    <t>2023-03-31 17:46:06+00:00</t>
   </si>
   <si>
     <t>2023-04-30 09:03:59+00:00</t>
   </si>
   <si>
+    <t>2023-03-31 13:37:56+00:00</t>
+  </si>
+  <si>
+    <t>2023-05-31 23:07:07+00:00</t>
+  </si>
+  <si>
+    <t>2023-05-31 10:27:00+00:00</t>
+  </si>
+  <si>
+    <t>2023-03-31 17:53:32+00:00</t>
+  </si>
+  <si>
     <t>2023-01-29 10:57:15+00:00</t>
   </si>
   <si>
     <t>2023-03-31 12:15:41+00:00</t>
   </si>
   <si>
-    <t>2023-01-29 20:11:03+00:00</t>
+    <t>2023-05-31 08:50:56+00:00</t>
+  </si>
+  <si>
+    <t>2023-04-30 08:59:35+00:00</t>
+  </si>
+  <si>
+    <t>2023-03-31 20:00:48+00:00</t>
+  </si>
+  <si>
+    <t>2023-03-31 14:11:08+00:00</t>
+  </si>
+  <si>
+    <t>2023-03-31 19:30:02+00:00</t>
+  </si>
+  <si>
+    <t>2023-05-30 22:38:44+00:00</t>
+  </si>
+  <si>
+    <t>2023-03-31 19:20:28+00:00</t>
+  </si>
+  <si>
+    <t>2023-05-31 23:11:28+00:00</t>
+  </si>
+  <si>
+    <t>2023-01-31 09:54:02+00:00</t>
+  </si>
+  <si>
+    <t>2023-02-27 08:53:51+00:00</t>
+  </si>
+  <si>
+    <t>2023-02-28 09:27:40+00:00</t>
+  </si>
+  <si>
+    <t>2023-01-31 11:37:35+00:00</t>
+  </si>
+  <si>
+    <t>2023-05-30 21:57:10+00:00</t>
+  </si>
+  <si>
+    <t>2023-05-31 13:59:21+00:00</t>
+  </si>
+  <si>
+    <t>2023-02-28 09:29:52+00:00</t>
   </si>
   <si>
     <t>https://x.com/Wizarab10/status/1641789137744285700</t>
@@ -469,6 +1024,9 @@
     <t>https://x.com/Wizarab10/status/1652775309014446081</t>
   </si>
   <si>
+    <t>https://x.com/Wizarab10/status/1663862474418929667</t>
+  </si>
+  <si>
     <t>https://x.com/Wizarab10/status/1652610742292561921</t>
   </si>
   <si>
@@ -478,6 +1036,15 @@
     <t>https://x.com/Wizarab10/status/1652759568479588352</t>
   </si>
   <si>
+    <t>https://x.com/Wizarab10/status/1641778203978088448</t>
+  </si>
+  <si>
+    <t>https://x.com/Wizarab10/status/1641780741360025602</t>
+  </si>
+  <si>
+    <t>https://x.com/Wizarab10/status/1663882219486695424</t>
+  </si>
+  <si>
     <t>https://x.com/Wizarab10/status/1652608559660646400</t>
   </si>
   <si>
@@ -487,13 +1054,37 @@
     <t>https://x.com/Wizarab10/status/1641787210054660097</t>
   </si>
   <si>
+    <t>https://x.com/Wizarab10/status/1664054075162341376</t>
+  </si>
+  <si>
+    <t>https://x.com/Wizarab10/status/1663852815511429120</t>
+  </si>
+  <si>
+    <t>https://x.com/Wizarab10/status/1652613172400988160</t>
+  </si>
+  <si>
+    <t>https://x.com/Wizarab10/status/1663681443803930624</t>
+  </si>
+  <si>
     <t>https://x.com/Wizarab10/status/1652792458181263360</t>
   </si>
   <si>
+    <t>https://x.com/Wizarab10/status/1663879826623610881</t>
+  </si>
+  <si>
+    <t>https://x.com/Wizarab10/status/1652605299235119104</t>
+  </si>
+  <si>
+    <t>https://x.com/Wizarab10/status/1652627404483883011</t>
+  </si>
+  <si>
     <t>https://x.com/Wizarab10/status/1652778262702039048</t>
   </si>
   <si>
-    <t>https://x.com/Wizarab10/status/1652627404483883011</t>
+    <t>https://x.com/Wizarab10/status/1664023601756897280</t>
+  </si>
+  <si>
+    <t>https://x.com/Wizarab10/status/1652610743580217344</t>
   </si>
   <si>
     <t>https://x.com/Wizarab10/status/1652632250100350977</t>
@@ -502,42 +1093,126 @@
     <t>https://x.com/Wizarab10/status/1619731584768442368</t>
   </si>
   <si>
+    <t>https://x.com/Wizarab10/status/1663874198048067584</t>
+  </si>
+  <si>
+    <t>https://x.com/Wizarab10/status/1641891151530676233</t>
+  </si>
+  <si>
+    <t>https://x.com/Wizarab10/status/1663858197310865409</t>
+  </si>
+  <si>
+    <t>https://x.com/Wizarab10/status/1663817389069283328</t>
+  </si>
+  <si>
     <t>https://x.com/Wizarab10/status/1652730128177278980</t>
   </si>
   <si>
+    <t>https://x.com/Wizarab10/status/1663864642567917569</t>
+  </si>
+  <si>
+    <t>https://x.com/Wizarab10/status/1652606997215182850</t>
+  </si>
+  <si>
+    <t>https://x.com/Wizarab10/status/1663863231159345154</t>
+  </si>
+  <si>
+    <t>https://x.com/Wizarab10/status/1663870801987215363</t>
+  </si>
+  <si>
+    <t>https://x.com/Wizarab10/status/1652604814889570304</t>
+  </si>
+  <si>
+    <t>https://x.com/Wizarab10/status/1652600422668828672</t>
+  </si>
+  <si>
     <t>https://x.com/Wizarab10/status/1641781412431814661</t>
   </si>
   <si>
-    <t>https://x.com/Wizarab10/status/1641895143627280396</t>
+    <t>https://x.com/Wizarab10/status/1663878777707847682</t>
   </si>
   <si>
     <t>https://x.com/Wizarab10/status/1619815811379765248</t>
   </si>
   <si>
+    <t>https://x.com/Wizarab10/status/1663668055447154689</t>
+  </si>
+  <si>
+    <t>https://x.com/Wizarab10/status/1630496483815354369</t>
+  </si>
+  <si>
+    <t>https://x.com/Wizarab10/status/1663672001817464832</t>
+  </si>
+  <si>
+    <t>https://x.com/Wizarab10/status/1663848693508833288</t>
+  </si>
+  <si>
+    <t>https://x.com/Wizarab10/status/1674843745735278599</t>
+  </si>
+  <si>
+    <t>https://x.com/Wizarab10/status/1630682714457112579</t>
+  </si>
+  <si>
+    <t>https://x.com/Wizarab10/status/1630514216699408386</t>
+  </si>
+  <si>
     <t>https://x.com/Wizarab10/status/1641810183281074183</t>
   </si>
   <si>
     <t>https://x.com/Wizarab10/status/1652652915511767041</t>
   </si>
   <si>
+    <t>https://x.com/Wizarab10/status/1652652784632594433</t>
+  </si>
+  <si>
     <t>https://x.com/Wizarab10/status/1641890521122578435</t>
   </si>
   <si>
+    <t>https://x.com/Wizarab10/status/1664055177198837760</t>
+  </si>
+  <si>
     <t>https://x.com/Wizarab10/status/1641760900993495041</t>
   </si>
   <si>
     <t>https://x.com/Wizarab10/status/1652637832043790337</t>
   </si>
   <si>
+    <t>https://x.com/Wizarab10/status/1652613288054726657</t>
+  </si>
+  <si>
+    <t>https://x.com/Wizarab10/status/1664044134611525634</t>
+  </si>
+  <si>
+    <t>https://x.com/Wizarab10/status/1652613708361736194</t>
+  </si>
+  <si>
+    <t>https://x.com/Wizarab10/status/1664043751918977026</t>
+  </si>
+  <si>
     <t>https://x.com/Wizarab10/status/1641800899814121474</t>
   </si>
   <si>
     <t>https://x.com/Wizarab10/status/1652597521510744064</t>
   </si>
   <si>
+    <t>https://x.com/Wizarab10/status/1664050449861734417</t>
+  </si>
+  <si>
+    <t>https://x.com/Wizarab10/status/1630158187318898688</t>
+  </si>
+  <si>
+    <t>https://x.com/Wizarab10/status/1663849151526850561</t>
+  </si>
+  <si>
     <t>https://x.com/Wizarab10/status/1620358713474433024</t>
   </si>
   <si>
+    <t>https://x.com/Wizarab10/status/1664016526393987073</t>
+  </si>
+  <si>
+    <t>https://x.com/Wizarab10/status/1620148976233361408</t>
+  </si>
+  <si>
     <t>https://x.com/Wizarab10/status/1652611840378126336</t>
   </si>
   <si>
@@ -547,19 +1222,82 @@
     <t>https://x.com/Wizarab10/status/1641780775753269248</t>
   </si>
   <si>
-    <t>https://x.com/Wizarab10/status/1641893668503146501</t>
+    <t>https://x.com/Wizarab10/status/1652758073541292032</t>
+  </si>
+  <si>
+    <t>https://x.com/Wizarab10/status/1664037638863454208</t>
+  </si>
+  <si>
+    <t>https://x.com/Wizarab10/status/1663815755425619971</t>
+  </si>
+  <si>
+    <t>https://x.com/Wizarab10/status/1641859429220900867</t>
   </si>
   <si>
     <t>https://x.com/Wizarab10/status/1652599667190906881</t>
   </si>
   <si>
+    <t>https://x.com/Wizarab10/status/1641796973115187205</t>
+  </si>
+  <si>
+    <t>https://x.com/Wizarab10/status/1664045875650330626</t>
+  </si>
+  <si>
+    <t>https://x.com/Wizarab10/status/1663854586484883459</t>
+  </si>
+  <si>
+    <t>https://x.com/Wizarab10/status/1641861300375412740</t>
+  </si>
+  <si>
     <t>https://x.com/Wizarab10/status/1619650876221829121</t>
   </si>
   <si>
     <t>https://x.com/Wizarab10/status/1641776275877507073</t>
   </si>
   <si>
-    <t>https://x.com/Wizarab10/status/1619790245050089473</t>
+    <t>https://x.com/Wizarab10/status/1663830408746741760</t>
+  </si>
+  <si>
+    <t>https://x.com/Wizarab10/status/1652598563031973890</t>
+  </si>
+  <si>
+    <t>https://x.com/Wizarab10/status/1641893325061120000</t>
+  </si>
+  <si>
+    <t>https://x.com/Wizarab10/status/1641805331394187264</t>
+  </si>
+  <si>
+    <t>https://x.com/Wizarab10/status/1641885581574647808</t>
+  </si>
+  <si>
+    <t>https://x.com/Wizarab10/status/1663676344117411841</t>
+  </si>
+  <si>
+    <t>https://x.com/Wizarab10/status/1641883176019677187</t>
+  </si>
+  <si>
+    <t>https://x.com/Wizarab10/status/1664046968379768834</t>
+  </si>
+  <si>
+    <t>https://x.com/Wizarab10/status/1620359745596186625</t>
+  </si>
+  <si>
+    <t>https://x.com/Wizarab10/status/1630129069965602822</t>
+  </si>
+  <si>
+    <t>https://x.com/Wizarab10/status/1630499970343116800</t>
+  </si>
+  <si>
+    <t>https://x.com/Wizarab10/status/1620385801858347009</t>
+  </si>
+  <si>
+    <t>https://x.com/Wizarab10/status/1663665881333874689</t>
+  </si>
+  <si>
+    <t>https://x.com/Wizarab10/status/1663908022769401862</t>
+  </si>
+  <si>
+    <t>https://x.com/Wizarab10/status/1630500521533493252</t>
   </si>
 </sst>
 </file>
@@ -930,7 +1668,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N40"/>
+  <dimension ref="A1:N101"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:14">
@@ -991,22 +1729,22 @@
         <v>1</v>
       </c>
       <c r="E2">
-        <v>0.3910011619307744</v>
+        <v>0.3908179469083004</v>
       </c>
       <c r="F2" t="s">
-        <v>53</v>
+        <v>114</v>
       </c>
       <c r="G2" t="b">
         <v>1</v>
       </c>
       <c r="H2" t="s">
-        <v>65</v>
+        <v>129</v>
       </c>
       <c r="I2">
-        <v>0.999999998945999</v>
+        <v>0.9999999989454046</v>
       </c>
       <c r="J2" t="s">
-        <v>104</v>
+        <v>229</v>
       </c>
       <c r="K2">
         <v>339</v>
@@ -1018,7 +1756,7 @@
         <v>126</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>143</v>
+        <v>328</v>
       </c>
     </row>
     <row r="3" spans="1:14">
@@ -1035,22 +1773,22 @@
         <v>1</v>
       </c>
       <c r="E3">
-        <v>0.38936333647025</v>
+        <v>0.3893656094529437</v>
       </c>
       <c r="F3" t="s">
-        <v>54</v>
+        <v>115</v>
       </c>
       <c r="G3" t="b">
         <v>1</v>
       </c>
       <c r="H3" t="s">
-        <v>66</v>
+        <v>130</v>
       </c>
       <c r="I3">
-        <v>0.9982737293257254</v>
+        <v>0.9984683705218352</v>
       </c>
       <c r="J3" t="s">
-        <v>105</v>
+        <v>230</v>
       </c>
       <c r="K3">
         <v>71</v>
@@ -1062,7 +1800,7 @@
         <v>13</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>144</v>
+        <v>329</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -1079,22 +1817,22 @@
         <v>1</v>
       </c>
       <c r="E4">
-        <v>0.3863951033241894</v>
+        <v>0.3860442962040238</v>
       </c>
       <c r="F4" t="s">
-        <v>55</v>
+        <v>116</v>
       </c>
       <c r="G4" t="b">
         <v>1</v>
       </c>
       <c r="H4" t="s">
-        <v>67</v>
+        <v>131</v>
       </c>
       <c r="I4">
-        <v>0.995145208717496</v>
+        <v>0.9949657287929029</v>
       </c>
       <c r="J4" t="s">
-        <v>106</v>
+        <v>231</v>
       </c>
       <c r="K4">
         <v>102</v>
@@ -1106,7 +1844,7 @@
         <v>27</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>145</v>
+        <v>330</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -1123,22 +1861,22 @@
         <v>1</v>
       </c>
       <c r="E5">
-        <v>0.3651995221340215</v>
+        <v>0.3651447570916004</v>
       </c>
       <c r="F5" t="s">
-        <v>54</v>
+        <v>115</v>
       </c>
       <c r="G5" t="b">
         <v>1</v>
       </c>
       <c r="H5" t="s">
-        <v>68</v>
+        <v>132</v>
       </c>
       <c r="I5">
-        <v>0.9728050456326498</v>
+        <v>0.972925170638856</v>
       </c>
       <c r="J5" t="s">
-        <v>107</v>
+        <v>232</v>
       </c>
       <c r="K5">
         <v>117</v>
@@ -1150,7 +1888,7 @@
         <v>9</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>146</v>
+        <v>331</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -1167,22 +1905,22 @@
         <v>1</v>
       </c>
       <c r="E6">
-        <v>0.3556246284455442</v>
+        <v>0.3558652367033284</v>
       </c>
       <c r="F6" t="s">
-        <v>54</v>
+        <v>115</v>
       </c>
       <c r="G6" t="b">
         <v>1</v>
       </c>
       <c r="H6" t="s">
-        <v>69</v>
+        <v>133</v>
       </c>
       <c r="I6">
-        <v>0.9627130984196207</v>
+        <v>0.9631390309704556</v>
       </c>
       <c r="J6" t="s">
-        <v>108</v>
+        <v>233</v>
       </c>
       <c r="K6">
         <v>108</v>
@@ -1194,7 +1932,7 @@
         <v>19</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>147</v>
+        <v>332</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -1211,22 +1949,22 @@
         <v>1</v>
       </c>
       <c r="E7">
-        <v>0.3545569756384044</v>
+        <v>0.3545134808117897</v>
       </c>
       <c r="F7" t="s">
-        <v>54</v>
+        <v>115</v>
       </c>
       <c r="G7" t="b">
         <v>1</v>
       </c>
       <c r="H7" t="s">
-        <v>70</v>
+        <v>134</v>
       </c>
       <c r="I7">
-        <v>0.9615877913277557</v>
+        <v>0.9617134754030688</v>
       </c>
       <c r="J7" t="s">
-        <v>109</v>
+        <v>234</v>
       </c>
       <c r="K7">
         <v>259</v>
@@ -1238,7 +1976,7 @@
         <v>60</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>148</v>
+        <v>333</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -1255,22 +1993,22 @@
         <v>1</v>
       </c>
       <c r="E8">
-        <v>0.3473998494052819</v>
+        <v>0.3473869192025311</v>
       </c>
       <c r="F8" t="s">
-        <v>54</v>
+        <v>115</v>
       </c>
       <c r="G8" t="b">
         <v>1</v>
       </c>
       <c r="H8" t="s">
-        <v>71</v>
+        <v>135</v>
       </c>
       <c r="I8">
-        <v>0.9540441733522809</v>
+        <v>0.954197836194839</v>
       </c>
       <c r="J8" t="s">
-        <v>110</v>
+        <v>235</v>
       </c>
       <c r="K8">
         <v>578</v>
@@ -1282,7 +2020,7 @@
         <v>238</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>149</v>
+        <v>334</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -1299,22 +2037,22 @@
         <v>1</v>
       </c>
       <c r="E9">
-        <v>0.3428113898761126</v>
+        <v>0.3426858885929382</v>
       </c>
       <c r="F9" t="s">
-        <v>54</v>
+        <v>115</v>
       </c>
       <c r="G9" t="b">
         <v>1</v>
       </c>
       <c r="H9" t="s">
-        <v>72</v>
+        <v>136</v>
       </c>
       <c r="I9">
-        <v>0.9492079325684042</v>
+        <v>0.9492401508613334</v>
       </c>
       <c r="J9" t="s">
-        <v>111</v>
+        <v>236</v>
       </c>
       <c r="K9">
         <v>149</v>
@@ -1326,7 +2064,7 @@
         <v>40</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>150</v>
+        <v>335</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -1337,40 +2075,40 @@
         <v>22</v>
       </c>
       <c r="C10">
-        <v>54</v>
+        <v>20</v>
       </c>
       <c r="D10" t="b">
         <v>1</v>
       </c>
       <c r="E10">
-        <v>0.3418055920238506</v>
+        <v>0.3419833013967912</v>
       </c>
       <c r="F10" t="s">
-        <v>54</v>
+        <v>117</v>
       </c>
       <c r="G10" t="b">
         <v>1</v>
       </c>
       <c r="H10" t="s">
-        <v>73</v>
+        <v>137</v>
       </c>
       <c r="I10">
-        <v>0.9481478206588357</v>
+        <v>0.9484992056246148</v>
       </c>
       <c r="J10" t="s">
-        <v>112</v>
+        <v>237</v>
       </c>
       <c r="K10">
-        <v>872</v>
+        <v>110</v>
       </c>
       <c r="L10">
-        <v>81</v>
+        <v>10</v>
       </c>
       <c r="M10">
-        <v>156</v>
+        <v>10</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>151</v>
+        <v>336</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -1381,40 +2119,40 @@
         <v>23</v>
       </c>
       <c r="C11">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="D11" t="b">
         <v>1</v>
       </c>
       <c r="E11">
-        <v>0.3413929409390743</v>
+        <v>0.3418140257426997</v>
       </c>
       <c r="F11" t="s">
-        <v>54</v>
+        <v>115</v>
       </c>
       <c r="G11" t="b">
         <v>1</v>
       </c>
       <c r="H11" t="s">
-        <v>74</v>
+        <v>138</v>
       </c>
       <c r="I11">
-        <v>0.9477128860161699</v>
+        <v>0.9483206882956919</v>
       </c>
       <c r="J11" t="s">
-        <v>113</v>
+        <v>238</v>
       </c>
       <c r="K11">
-        <v>27</v>
+        <v>872</v>
       </c>
       <c r="L11">
-        <v>1</v>
+        <v>81</v>
       </c>
       <c r="M11">
-        <v>0</v>
+        <v>156</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>152</v>
+        <v>337</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -1425,40 +2163,40 @@
         <v>24</v>
       </c>
       <c r="C12">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="D12" t="b">
         <v>1</v>
       </c>
       <c r="E12">
-        <v>0.333345229622111</v>
+        <v>0.3413486729249449</v>
       </c>
       <c r="F12" t="s">
-        <v>54</v>
+        <v>115</v>
       </c>
       <c r="G12" t="b">
         <v>1</v>
       </c>
       <c r="H12" t="s">
-        <v>75</v>
+        <v>139</v>
       </c>
       <c r="I12">
-        <v>0.939230590500531</v>
+        <v>0.9478299293470519</v>
       </c>
       <c r="J12" t="s">
-        <v>114</v>
+        <v>239</v>
       </c>
       <c r="K12">
-        <v>103</v>
+        <v>27</v>
       </c>
       <c r="L12">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="M12">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>153</v>
+        <v>338</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -1469,40 +2207,40 @@
         <v>25</v>
       </c>
       <c r="C13">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="D13" t="b">
         <v>1</v>
       </c>
       <c r="E13">
-        <v>0.3188308458723301</v>
+        <v>0.3332522084900151</v>
       </c>
       <c r="F13" t="s">
-        <v>56</v>
+        <v>115</v>
       </c>
       <c r="G13" t="b">
         <v>1</v>
       </c>
       <c r="H13" t="s">
-        <v>76</v>
+        <v>140</v>
       </c>
       <c r="I13">
-        <v>0.9239324159830726</v>
+        <v>0.9392914350644594</v>
       </c>
       <c r="J13" t="s">
-        <v>115</v>
+        <v>240</v>
       </c>
       <c r="K13">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="L13">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M13">
         <v>14</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>154</v>
+        <v>339</v>
       </c>
     </row>
     <row r="14" spans="1:14">
@@ -1513,40 +2251,40 @@
         <v>26</v>
       </c>
       <c r="C14">
-        <v>52</v>
+        <v>27</v>
       </c>
       <c r="D14" t="b">
         <v>1</v>
       </c>
       <c r="E14">
-        <v>0.3174615390326933</v>
+        <v>0.3270232494910824</v>
       </c>
       <c r="F14" t="s">
-        <v>57</v>
+        <v>118</v>
       </c>
       <c r="G14" t="b">
         <v>1</v>
       </c>
       <c r="H14" t="s">
-        <v>77</v>
+        <v>141</v>
       </c>
       <c r="I14">
-        <v>0.9224891652490529</v>
+        <v>0.9327224034548801</v>
       </c>
       <c r="J14" t="s">
-        <v>116</v>
+        <v>241</v>
       </c>
       <c r="K14">
-        <v>398</v>
+        <v>34</v>
       </c>
       <c r="L14">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="M14">
-        <v>117</v>
+        <v>1</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>155</v>
+        <v>340</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -1557,40 +2295,40 @@
         <v>27</v>
       </c>
       <c r="C15">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="D15" t="b">
         <v>1</v>
       </c>
       <c r="E15">
-        <v>0.3105686964048006</v>
+        <v>0.3258560747103073</v>
       </c>
       <c r="F15" t="s">
-        <v>56</v>
+        <v>119</v>
       </c>
       <c r="G15" t="b">
         <v>1</v>
       </c>
       <c r="H15" t="s">
-        <v>78</v>
+        <v>142</v>
       </c>
       <c r="I15">
-        <v>0.9152241024492307</v>
+        <v>0.9314915062808692</v>
       </c>
       <c r="J15" t="s">
-        <v>117</v>
+        <v>242</v>
       </c>
       <c r="K15">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="L15">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="M15">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>156</v>
+        <v>341</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -1601,40 +2339,40 @@
         <v>28</v>
       </c>
       <c r="C16">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D16" t="b">
         <v>1</v>
       </c>
       <c r="E16">
-        <v>0.2837880242647121</v>
+        <v>0.3190639585765452</v>
       </c>
       <c r="F16" t="s">
-        <v>57</v>
+        <v>114</v>
       </c>
       <c r="G16" t="b">
         <v>1</v>
       </c>
       <c r="H16" t="s">
-        <v>79</v>
+        <v>143</v>
       </c>
       <c r="I16">
-        <v>0.8869972480986218</v>
+        <v>0.9243285717381532</v>
       </c>
       <c r="J16" t="s">
-        <v>118</v>
+        <v>243</v>
       </c>
       <c r="K16">
-        <v>2814</v>
+        <v>391</v>
       </c>
       <c r="L16">
-        <v>113</v>
+        <v>186</v>
       </c>
       <c r="M16">
-        <v>739</v>
+        <v>69</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>157</v>
+        <v>342</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -1645,40 +2383,40 @@
         <v>29</v>
       </c>
       <c r="C17">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="D17" t="b">
         <v>1</v>
       </c>
       <c r="E17">
-        <v>0.2809698977778796</v>
+        <v>0.318845448081383</v>
       </c>
       <c r="F17" t="s">
-        <v>58</v>
+        <v>119</v>
       </c>
       <c r="G17" t="b">
         <v>1</v>
       </c>
       <c r="H17" t="s">
-        <v>80</v>
+        <v>144</v>
       </c>
       <c r="I17">
-        <v>0.8840269400544731</v>
+        <v>0.9240981315715072</v>
       </c>
       <c r="J17" t="s">
-        <v>119</v>
+        <v>244</v>
       </c>
       <c r="K17">
-        <v>125</v>
+        <v>86</v>
       </c>
       <c r="L17">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="M17">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>158</v>
+        <v>343</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1689,40 +2427,40 @@
         <v>30</v>
       </c>
       <c r="C18">
-        <v>9</v>
+        <v>52</v>
       </c>
       <c r="D18" t="b">
         <v>1</v>
       </c>
       <c r="E18">
-        <v>0.2806184849162</v>
+        <v>0.3175331830861279</v>
       </c>
       <c r="F18" t="s">
-        <v>53</v>
+        <v>120</v>
       </c>
       <c r="G18" t="b">
         <v>1</v>
       </c>
       <c r="H18" t="s">
-        <v>81</v>
+        <v>145</v>
       </c>
       <c r="I18">
-        <v>0.8836565505582098</v>
+        <v>0.922714222922333</v>
       </c>
       <c r="J18" t="s">
-        <v>120</v>
+        <v>245</v>
       </c>
       <c r="K18">
-        <v>180</v>
+        <v>398</v>
       </c>
       <c r="L18">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M18">
-        <v>25</v>
+        <v>117</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>159</v>
+        <v>344</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1733,40 +2471,40 @@
         <v>31</v>
       </c>
       <c r="C19">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="D19" t="b">
         <v>1</v>
       </c>
       <c r="E19">
-        <v>0.2625656839534497</v>
+        <v>0.3105163367417204</v>
       </c>
       <c r="F19" t="s">
-        <v>59</v>
+        <v>119</v>
       </c>
       <c r="G19" t="b">
         <v>1</v>
       </c>
       <c r="H19" t="s">
-        <v>82</v>
+        <v>146</v>
       </c>
       <c r="I19">
-        <v>0.8646288808742479</v>
+        <v>0.9153142889295304</v>
       </c>
       <c r="J19" t="s">
-        <v>121</v>
+        <v>246</v>
       </c>
       <c r="K19">
-        <v>112</v>
+        <v>51</v>
       </c>
       <c r="L19">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="M19">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>160</v>
+        <v>345</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1777,40 +2515,40 @@
         <v>32</v>
       </c>
       <c r="C20">
-        <v>15</v>
+        <v>52</v>
       </c>
       <c r="D20" t="b">
         <v>1</v>
       </c>
       <c r="E20">
-        <v>0.2617185593364111</v>
+        <v>0.3095670915407471</v>
       </c>
       <c r="F20" t="s">
-        <v>60</v>
+        <v>115</v>
       </c>
       <c r="G20" t="b">
         <v>1</v>
       </c>
       <c r="H20" t="s">
-        <v>83</v>
+        <v>147</v>
       </c>
       <c r="I20">
-        <v>0.8637360107081489</v>
+        <v>0.9143132192914893</v>
       </c>
       <c r="J20" t="s">
-        <v>122</v>
+        <v>247</v>
       </c>
       <c r="K20">
-        <v>102</v>
+        <v>1170</v>
       </c>
       <c r="L20">
-        <v>17</v>
+        <v>465</v>
       </c>
       <c r="M20">
-        <v>21</v>
+        <v>281</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>161</v>
+        <v>346</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1821,40 +2559,40 @@
         <v>33</v>
       </c>
       <c r="C21">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="D21" t="b">
         <v>1</v>
       </c>
       <c r="E21">
-        <v>0.2486901203763698</v>
+        <v>0.299691429752608</v>
       </c>
       <c r="F21" t="s">
-        <v>56</v>
+        <v>119</v>
       </c>
       <c r="G21" t="b">
         <v>1</v>
       </c>
       <c r="H21" t="s">
-        <v>84</v>
+        <v>148</v>
       </c>
       <c r="I21">
-        <v>0.8500040234369859</v>
+        <v>0.9038983916352281</v>
       </c>
       <c r="J21" t="s">
-        <v>123</v>
+        <v>248</v>
       </c>
       <c r="K21">
-        <v>257</v>
+        <v>86</v>
       </c>
       <c r="L21">
-        <v>64</v>
+        <v>24</v>
       </c>
       <c r="M21">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>162</v>
+        <v>347</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1865,40 +2603,40 @@
         <v>34</v>
       </c>
       <c r="C22">
-        <v>49</v>
+        <v>15</v>
       </c>
       <c r="D22" t="b">
         <v>1</v>
       </c>
       <c r="E22">
-        <v>0.2270186730893146</v>
+        <v>0.2991892723682146</v>
       </c>
       <c r="F22" t="s">
-        <v>61</v>
+        <v>115</v>
       </c>
       <c r="G22" t="b">
         <v>1</v>
       </c>
       <c r="H22" t="s">
-        <v>85</v>
+        <v>149</v>
       </c>
       <c r="I22">
-        <v>0.8271622970255375</v>
+        <v>0.9033688187593063</v>
       </c>
       <c r="J22" t="s">
-        <v>124</v>
+        <v>249</v>
       </c>
       <c r="K22">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="L22">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="M22">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>163</v>
+        <v>348</v>
       </c>
     </row>
     <row r="23" spans="1:14">
@@ -1909,40 +2647,40 @@
         <v>35</v>
       </c>
       <c r="C23">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="D23" t="b">
         <v>1</v>
       </c>
       <c r="E23">
-        <v>0.2175885700966405</v>
+        <v>0.2969316412619682</v>
       </c>
       <c r="F23" t="s">
-        <v>54</v>
+        <v>115</v>
       </c>
       <c r="G23" t="b">
         <v>1</v>
       </c>
       <c r="H23" t="s">
-        <v>86</v>
+        <v>150</v>
       </c>
       <c r="I23">
-        <v>0.817222959345995</v>
+        <v>0.9009879313426059</v>
       </c>
       <c r="J23" t="s">
-        <v>125</v>
+        <v>250</v>
       </c>
       <c r="K23">
-        <v>18</v>
+        <v>347</v>
       </c>
       <c r="L23">
-        <v>2</v>
+        <v>56</v>
       </c>
       <c r="M23">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>164</v>
+        <v>349</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -1953,40 +2691,40 @@
         <v>36</v>
       </c>
       <c r="C24">
-        <v>12</v>
+        <v>52</v>
       </c>
       <c r="D24" t="b">
         <v>1</v>
       </c>
       <c r="E24">
-        <v>0.21311210848163</v>
+        <v>0.2838197198814175</v>
       </c>
       <c r="F24" t="s">
-        <v>62</v>
+        <v>120</v>
       </c>
       <c r="G24" t="b">
         <v>1</v>
       </c>
       <c r="H24" t="s">
-        <v>87</v>
+        <v>151</v>
       </c>
       <c r="I24">
-        <v>0.8125047644720191</v>
+        <v>0.8871601591537192</v>
       </c>
       <c r="J24" t="s">
-        <v>126</v>
+        <v>251</v>
       </c>
       <c r="K24">
-        <v>45</v>
+        <v>2814</v>
       </c>
       <c r="L24">
-        <v>3</v>
+        <v>113</v>
       </c>
       <c r="M24">
-        <v>8</v>
+        <v>739</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>165</v>
+        <v>350</v>
       </c>
     </row>
     <row r="25" spans="1:14">
@@ -1997,40 +2735,40 @@
         <v>37</v>
       </c>
       <c r="C25">
-        <v>9</v>
+        <v>45</v>
       </c>
       <c r="D25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E25">
-        <v>0.3757447734767477</v>
+        <v>0.2835443509860937</v>
       </c>
       <c r="F25" t="s">
-        <v>53</v>
+        <v>121</v>
       </c>
       <c r="G25" t="b">
         <v>1</v>
       </c>
       <c r="H25" t="s">
-        <v>88</v>
+        <v>152</v>
       </c>
       <c r="I25">
-        <v>0.733919750752247</v>
+        <v>0.8868697563788754</v>
       </c>
       <c r="J25" t="s">
-        <v>127</v>
+        <v>252</v>
       </c>
       <c r="K25">
-        <v>243</v>
+        <v>434</v>
       </c>
       <c r="L25">
-        <v>8</v>
+        <v>104</v>
       </c>
       <c r="M25">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>166</v>
+        <v>351</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -2041,40 +2779,40 @@
         <v>38</v>
       </c>
       <c r="C26">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E26">
-        <v>0.3726030076480706</v>
+        <v>0.2814306903510778</v>
       </c>
       <c r="F26" t="s">
-        <v>56</v>
+        <v>115</v>
       </c>
       <c r="G26" t="b">
         <v>1</v>
       </c>
       <c r="H26" t="s">
-        <v>89</v>
+        <v>153</v>
       </c>
       <c r="I26">
-        <v>0.7306083265286168</v>
+        <v>0.8846406995612399</v>
       </c>
       <c r="J26" t="s">
-        <v>128</v>
+        <v>253</v>
       </c>
       <c r="K26">
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="L26">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="M26">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>167</v>
+        <v>352</v>
       </c>
     </row>
     <row r="27" spans="1:14">
@@ -2085,40 +2823,40 @@
         <v>39</v>
       </c>
       <c r="C27">
-        <v>54</v>
+        <v>9</v>
       </c>
       <c r="D27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E27">
-        <v>0.3665418298403278</v>
+        <v>0.280631714987409</v>
       </c>
       <c r="F27" t="s">
-        <v>53</v>
+        <v>114</v>
       </c>
       <c r="G27" t="b">
         <v>1</v>
       </c>
       <c r="H27" t="s">
-        <v>90</v>
+        <v>154</v>
       </c>
       <c r="I27">
-        <v>0.7242198392540127</v>
+        <v>0.883798103804852</v>
       </c>
       <c r="J27" t="s">
-        <v>129</v>
+        <v>254</v>
       </c>
       <c r="K27">
-        <v>191</v>
+        <v>180</v>
       </c>
       <c r="L27">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="M27">
-        <v>59</v>
+        <v>25</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>168</v>
+        <v>353</v>
       </c>
     </row>
     <row r="28" spans="1:14">
@@ -2129,40 +2867,40 @@
         <v>40</v>
       </c>
       <c r="C28">
-        <v>5</v>
+        <v>48</v>
       </c>
       <c r="D28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E28">
-        <v>0.3204366613092677</v>
+        <v>0.28042589151681</v>
       </c>
       <c r="F28" t="s">
-        <v>63</v>
+        <v>118</v>
       </c>
       <c r="G28" t="b">
         <v>1</v>
       </c>
       <c r="H28" t="s">
-        <v>91</v>
+        <v>155</v>
       </c>
       <c r="I28">
-        <v>0.6756249470075104</v>
+        <v>0.8835810433161588</v>
       </c>
       <c r="J28" t="s">
-        <v>130</v>
+        <v>255</v>
       </c>
       <c r="K28">
-        <v>66</v>
+        <v>125</v>
       </c>
       <c r="L28">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="M28">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>169</v>
+        <v>354</v>
       </c>
     </row>
     <row r="29" spans="1:14">
@@ -2173,40 +2911,40 @@
         <v>41</v>
       </c>
       <c r="C29">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="D29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E29">
-        <v>0.3193288097767228</v>
+        <v>0.276416406656705</v>
       </c>
       <c r="F29" t="s">
-        <v>59</v>
+        <v>122</v>
       </c>
       <c r="G29" t="b">
         <v>1</v>
       </c>
       <c r="H29" t="s">
-        <v>92</v>
+        <v>156</v>
       </c>
       <c r="I29">
-        <v>0.6744572704201692</v>
+        <v>0.8793526589603343</v>
       </c>
       <c r="J29" t="s">
-        <v>131</v>
+        <v>256</v>
       </c>
       <c r="K29">
-        <v>822</v>
+        <v>1038</v>
       </c>
       <c r="L29">
-        <v>525</v>
+        <v>30</v>
       </c>
       <c r="M29">
-        <v>353</v>
+        <v>324</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>170</v>
+        <v>355</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -2217,40 +2955,40 @@
         <v>42</v>
       </c>
       <c r="C30">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="D30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E30">
-        <v>0.2898028209002732</v>
+        <v>0.2720670216463877</v>
       </c>
       <c r="F30" t="s">
-        <v>59</v>
+        <v>115</v>
       </c>
       <c r="G30" t="b">
         <v>1</v>
       </c>
       <c r="H30" t="s">
-        <v>93</v>
+        <v>157</v>
       </c>
       <c r="I30">
-        <v>0.6433368495728645</v>
+        <v>0.8747658174640425</v>
       </c>
       <c r="J30" t="s">
-        <v>132</v>
+        <v>238</v>
       </c>
       <c r="K30">
-        <v>45</v>
+        <v>243</v>
       </c>
       <c r="L30">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M30">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>171</v>
+        <v>356</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -2261,40 +2999,40 @@
         <v>43</v>
       </c>
       <c r="C31">
+        <v>53</v>
+      </c>
+      <c r="D31" t="b">
+        <v>1</v>
+      </c>
+      <c r="E31">
+        <v>0.2629394247452055</v>
+      </c>
+      <c r="F31" t="s">
+        <v>121</v>
+      </c>
+      <c r="G31" t="b">
+        <v>1</v>
+      </c>
+      <c r="H31" t="s">
+        <v>158</v>
+      </c>
+      <c r="I31">
+        <v>0.8651398956087792</v>
+      </c>
+      <c r="J31" t="s">
+        <v>257</v>
+      </c>
+      <c r="K31">
+        <v>112</v>
+      </c>
+      <c r="L31">
+        <v>4</v>
+      </c>
+      <c r="M31">
         <v>31</v>
       </c>
-      <c r="D31" t="b">
-        <v>0</v>
-      </c>
-      <c r="E31">
-        <v>0.2809537324056162</v>
-      </c>
-      <c r="F31" t="s">
-        <v>59</v>
-      </c>
-      <c r="G31" t="b">
-        <v>1</v>
-      </c>
-      <c r="H31" t="s">
-        <v>94</v>
-      </c>
-      <c r="I31">
-        <v>0.6340099017364647</v>
-      </c>
-      <c r="J31" t="s">
-        <v>133</v>
-      </c>
-      <c r="K31">
-        <v>177</v>
-      </c>
-      <c r="L31">
-        <v>66</v>
-      </c>
-      <c r="M31">
-        <v>55</v>
-      </c>
       <c r="N31" s="2" t="s">
-        <v>172</v>
+        <v>357</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -2308,37 +3046,37 @@
         <v>15</v>
       </c>
       <c r="D32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E32">
-        <v>0.2623390232322111</v>
+        <v>0.2620273708301225</v>
       </c>
       <c r="F32" t="s">
-        <v>55</v>
+        <v>123</v>
       </c>
       <c r="G32" t="b">
         <v>1</v>
       </c>
       <c r="H32" t="s">
-        <v>95</v>
+        <v>159</v>
       </c>
       <c r="I32">
-        <v>0.6143899802547289</v>
+        <v>0.86417804773037</v>
       </c>
       <c r="J32" t="s">
-        <v>134</v>
+        <v>258</v>
       </c>
       <c r="K32">
-        <v>61</v>
+        <v>102</v>
       </c>
       <c r="L32">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="M32">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>173</v>
+        <v>358</v>
       </c>
     </row>
     <row r="33" spans="1:14">
@@ -2349,40 +3087,40 @@
         <v>45</v>
       </c>
       <c r="C33">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="D33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E33">
-        <v>0.2538645528760656</v>
+        <v>0.2591568991808191</v>
       </c>
       <c r="F33" t="s">
-        <v>59</v>
+        <v>115</v>
       </c>
       <c r="G33" t="b">
         <v>1</v>
       </c>
       <c r="H33" t="s">
-        <v>96</v>
+        <v>160</v>
       </c>
       <c r="I33">
-        <v>0.6054578802988282</v>
+        <v>0.861150861485942</v>
       </c>
       <c r="J33" t="s">
-        <v>135</v>
+        <v>259</v>
       </c>
       <c r="K33">
-        <v>114</v>
+        <v>304</v>
       </c>
       <c r="L33">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M33">
-        <v>13</v>
+        <v>89</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>174</v>
+        <v>359</v>
       </c>
     </row>
     <row r="34" spans="1:14">
@@ -2393,40 +3131,40 @@
         <v>46</v>
       </c>
       <c r="C34">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="D34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E34">
-        <v>0.2530010010643271</v>
+        <v>0.2584892121702487</v>
       </c>
       <c r="F34" t="s">
-        <v>54</v>
+        <v>114</v>
       </c>
       <c r="G34" t="b">
         <v>1</v>
       </c>
       <c r="H34" t="s">
-        <v>97</v>
+        <v>161</v>
       </c>
       <c r="I34">
-        <v>0.6045476958536193</v>
+        <v>0.8604467218249658</v>
       </c>
       <c r="J34" t="s">
-        <v>136</v>
+        <v>260</v>
       </c>
       <c r="K34">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="L34">
         <v>2</v>
       </c>
       <c r="M34">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>175</v>
+        <v>360</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -2437,40 +3175,40 @@
         <v>47</v>
       </c>
       <c r="C35">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="D35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E35">
-        <v>0.2525755444620978</v>
+        <v>0.2520298186053447</v>
       </c>
       <c r="F35" t="s">
-        <v>54</v>
+        <v>115</v>
       </c>
       <c r="G35" t="b">
         <v>1</v>
       </c>
       <c r="H35" t="s">
-        <v>98</v>
+        <v>162</v>
       </c>
       <c r="I35">
-        <v>0.6040992641831666</v>
+        <v>0.8536346749783197</v>
       </c>
       <c r="J35" t="s">
-        <v>137</v>
+        <v>261</v>
       </c>
       <c r="K35">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="L35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M35">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>176</v>
+        <v>361</v>
       </c>
     </row>
     <row r="36" spans="1:14">
@@ -2481,40 +3219,40 @@
         <v>48</v>
       </c>
       <c r="C36">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="D36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E36">
-        <v>0.2436959067018075</v>
+        <v>0.2488197037790032</v>
       </c>
       <c r="F36" t="s">
-        <v>59</v>
+        <v>121</v>
       </c>
       <c r="G36" t="b">
         <v>1</v>
       </c>
       <c r="H36" t="s">
-        <v>99</v>
+        <v>163</v>
       </c>
       <c r="I36">
-        <v>0.5947401173912275</v>
+        <v>0.8502493025961561</v>
       </c>
       <c r="J36" t="s">
-        <v>138</v>
+        <v>262</v>
       </c>
       <c r="K36">
-        <v>71</v>
+        <v>111</v>
       </c>
       <c r="L36">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M36">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>177</v>
+        <v>362</v>
       </c>
     </row>
     <row r="37" spans="1:14">
@@ -2525,40 +3263,40 @@
         <v>49</v>
       </c>
       <c r="C37">
-        <v>49</v>
+        <v>12</v>
       </c>
       <c r="D37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E37">
-        <v>0.2225429789569603</v>
+        <v>0.2486754221069533</v>
       </c>
       <c r="F37" t="s">
-        <v>63</v>
+        <v>119</v>
       </c>
       <c r="G37" t="b">
         <v>1</v>
       </c>
       <c r="H37" t="s">
-        <v>100</v>
+        <v>164</v>
       </c>
       <c r="I37">
-        <v>0.572444911079024</v>
+        <v>0.8500971438061334</v>
       </c>
       <c r="J37" t="s">
-        <v>139</v>
+        <v>263</v>
       </c>
       <c r="K37">
-        <v>67</v>
+        <v>257</v>
       </c>
       <c r="L37">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="M37">
-        <v>2</v>
+        <v>43</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>178</v>
+        <v>363</v>
       </c>
     </row>
     <row r="38" spans="1:14">
@@ -2569,40 +3307,40 @@
         <v>50</v>
       </c>
       <c r="C38">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="D38" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E38">
-        <v>0.2060586137606017</v>
+        <v>0.2460126996141363</v>
       </c>
       <c r="F38" t="s">
-        <v>59</v>
+        <v>115</v>
       </c>
       <c r="G38" t="b">
         <v>1</v>
       </c>
       <c r="H38" t="s">
-        <v>101</v>
+        <v>165</v>
       </c>
       <c r="I38">
-        <v>0.5550703742105731</v>
+        <v>0.8472890488699089</v>
       </c>
       <c r="J38" t="s">
-        <v>140</v>
+        <v>264</v>
       </c>
       <c r="K38">
-        <v>480</v>
+        <v>53</v>
       </c>
       <c r="L38">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="M38">
-        <v>163</v>
+        <v>4</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>179</v>
+        <v>364</v>
       </c>
     </row>
     <row r="39" spans="1:14">
@@ -2613,40 +3351,40 @@
         <v>51</v>
       </c>
       <c r="C39">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="D39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E39">
-        <v>0.2025802526074246</v>
+        <v>0.2441192474003221</v>
       </c>
       <c r="F39" t="s">
-        <v>58</v>
+        <v>119</v>
       </c>
       <c r="G39" t="b">
         <v>1</v>
       </c>
       <c r="H39" t="s">
-        <v>102</v>
+        <v>166</v>
       </c>
       <c r="I39">
-        <v>0.5514041781892054</v>
+        <v>0.8452922228439381</v>
       </c>
       <c r="J39" t="s">
-        <v>141</v>
+        <v>265</v>
       </c>
       <c r="K39">
-        <v>459</v>
+        <v>211</v>
       </c>
       <c r="L39">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="M39">
-        <v>148</v>
+        <v>40</v>
       </c>
       <c r="N39" s="2" t="s">
-        <v>180</v>
+        <v>365</v>
       </c>
     </row>
     <row r="40" spans="1:14">
@@ -2657,40 +3395,2724 @@
         <v>52</v>
       </c>
       <c r="C40">
+        <v>57</v>
+      </c>
+      <c r="D40" t="b">
+        <v>1</v>
+      </c>
+      <c r="E40">
+        <v>0.2385658467422767</v>
+      </c>
+      <c r="F40" t="s">
+        <v>115</v>
+      </c>
+      <c r="G40" t="b">
+        <v>1</v>
+      </c>
+      <c r="H40" t="s">
+        <v>167</v>
+      </c>
+      <c r="I40">
+        <v>0.8394356319642085</v>
+      </c>
+      <c r="J40" t="s">
+        <v>266</v>
+      </c>
+      <c r="K40">
+        <v>162</v>
+      </c>
+      <c r="L40">
+        <v>21</v>
+      </c>
+      <c r="M40">
+        <v>18</v>
+      </c>
+      <c r="N40" s="2" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41" t="s">
+        <v>53</v>
+      </c>
+      <c r="C41">
+        <v>14</v>
+      </c>
+      <c r="D41" t="b">
+        <v>1</v>
+      </c>
+      <c r="E41">
+        <v>0.2369224126457143</v>
+      </c>
+      <c r="F41" t="s">
+        <v>121</v>
+      </c>
+      <c r="G41" t="b">
+        <v>1</v>
+      </c>
+      <c r="H41" t="s">
+        <v>168</v>
+      </c>
+      <c r="I41">
+        <v>0.8377024738987229</v>
+      </c>
+      <c r="J41" t="s">
+        <v>267</v>
+      </c>
+      <c r="K41">
+        <v>202</v>
+      </c>
+      <c r="L41">
+        <v>21</v>
+      </c>
+      <c r="M41">
+        <v>25</v>
+      </c>
+      <c r="N41" s="2" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14">
+      <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="B42" t="s">
+        <v>54</v>
+      </c>
+      <c r="C42">
+        <v>24</v>
+      </c>
+      <c r="D42" t="b">
+        <v>1</v>
+      </c>
+      <c r="E42">
+        <v>0.2330657813273172</v>
+      </c>
+      <c r="F42" t="s">
+        <v>117</v>
+      </c>
+      <c r="G42" t="b">
+        <v>1</v>
+      </c>
+      <c r="H42" t="s">
+        <v>169</v>
+      </c>
+      <c r="I42">
+        <v>0.8336352881873729</v>
+      </c>
+      <c r="J42" t="s">
+        <v>268</v>
+      </c>
+      <c r="K42">
+        <v>0</v>
+      </c>
+      <c r="L42">
+        <v>1</v>
+      </c>
+      <c r="M42">
+        <v>0</v>
+      </c>
+      <c r="N42" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43" t="s">
+        <v>55</v>
+      </c>
+      <c r="C43">
+        <v>30</v>
+      </c>
+      <c r="D43" t="b">
+        <v>1</v>
+      </c>
+      <c r="E43">
+        <v>0.2302108915065116</v>
+      </c>
+      <c r="F43" t="s">
+        <v>121</v>
+      </c>
+      <c r="G43" t="b">
+        <v>1</v>
+      </c>
+      <c r="H43" t="s">
+        <v>170</v>
+      </c>
+      <c r="I43">
+        <v>0.8306245344678587</v>
+      </c>
+      <c r="J43" t="s">
+        <v>269</v>
+      </c>
+      <c r="K43">
+        <v>114</v>
+      </c>
+      <c r="L43">
+        <v>6</v>
+      </c>
+      <c r="M43">
+        <v>24</v>
+      </c>
+      <c r="N43" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14">
+      <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="B44" t="s">
+        <v>56</v>
+      </c>
+      <c r="C44">
+        <v>49</v>
+      </c>
+      <c r="D44" t="b">
+        <v>1</v>
+      </c>
+      <c r="E44">
+        <v>0.2270334715933246</v>
+      </c>
+      <c r="F44" t="s">
+        <v>124</v>
+      </c>
+      <c r="G44" t="b">
+        <v>1</v>
+      </c>
+      <c r="H44" t="s">
+        <v>171</v>
+      </c>
+      <c r="I44">
+        <v>0.8272736419912492</v>
+      </c>
+      <c r="J44" t="s">
+        <v>270</v>
+      </c>
+      <c r="K44">
+        <v>80</v>
+      </c>
+      <c r="L44">
+        <v>11</v>
+      </c>
+      <c r="M44">
+        <v>17</v>
+      </c>
+      <c r="N44" s="2" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14">
+      <c r="A45">
+        <v>44</v>
+      </c>
+      <c r="B45" t="s">
+        <v>57</v>
+      </c>
+      <c r="C45">
+        <v>50</v>
+      </c>
+      <c r="D45" t="b">
+        <v>1</v>
+      </c>
+      <c r="E45">
+        <v>0.2137466820934403</v>
+      </c>
+      <c r="F45" t="s">
+        <v>121</v>
+      </c>
+      <c r="G45" t="b">
+        <v>1</v>
+      </c>
+      <c r="H45" t="s">
+        <v>172</v>
+      </c>
+      <c r="I45">
+        <v>0.8132614546852286</v>
+      </c>
+      <c r="J45" t="s">
+        <v>271</v>
+      </c>
+      <c r="K45">
+        <v>1314</v>
+      </c>
+      <c r="L45">
+        <v>282</v>
+      </c>
+      <c r="M45">
+        <v>300</v>
+      </c>
+      <c r="N45" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14">
+      <c r="A46">
+        <v>45</v>
+      </c>
+      <c r="B46" t="s">
+        <v>58</v>
+      </c>
+      <c r="C46">
+        <v>12</v>
+      </c>
+      <c r="D46" t="b">
+        <v>1</v>
+      </c>
+      <c r="E46">
+        <v>0.2130994608438453</v>
+      </c>
+      <c r="F46" t="s">
+        <v>125</v>
+      </c>
+      <c r="G46" t="b">
+        <v>1</v>
+      </c>
+      <c r="H46" t="s">
+        <v>173</v>
+      </c>
+      <c r="I46">
+        <v>0.8125788981219715</v>
+      </c>
+      <c r="J46" t="s">
+        <v>272</v>
+      </c>
+      <c r="K46">
+        <v>45</v>
+      </c>
+      <c r="L46">
+        <v>3</v>
+      </c>
+      <c r="M46">
+        <v>8</v>
+      </c>
+      <c r="N46" s="2" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14">
+      <c r="A47">
         <v>46</v>
       </c>
-      <c r="D40" t="b">
-        <v>0</v>
-      </c>
-      <c r="E40">
-        <v>0.1861248419067052</v>
-      </c>
-      <c r="F40" t="s">
+      <c r="B47" t="s">
+        <v>59</v>
+      </c>
+      <c r="C47">
+        <v>35</v>
+      </c>
+      <c r="D47" t="b">
+        <v>1</v>
+      </c>
+      <c r="E47">
+        <v>0.2092557601662806</v>
+      </c>
+      <c r="F47" t="s">
+        <v>126</v>
+      </c>
+      <c r="G47" t="b">
+        <v>1</v>
+      </c>
+      <c r="H47" t="s">
+        <v>174</v>
+      </c>
+      <c r="I47">
+        <v>0.8085253490051751</v>
+      </c>
+      <c r="J47" t="s">
+        <v>273</v>
+      </c>
+      <c r="K47">
+        <v>63</v>
+      </c>
+      <c r="L47">
+        <v>13</v>
+      </c>
+      <c r="M47">
+        <v>8</v>
+      </c>
+      <c r="N47" s="2" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14">
+      <c r="A48">
+        <v>47</v>
+      </c>
+      <c r="B48" t="s">
+        <v>60</v>
+      </c>
+      <c r="C48">
+        <v>48</v>
+      </c>
+      <c r="D48" t="b">
+        <v>1</v>
+      </c>
+      <c r="E48">
+        <v>0.2091802951257</v>
+      </c>
+      <c r="F48" t="s">
+        <v>117</v>
+      </c>
+      <c r="G48" t="b">
+        <v>1</v>
+      </c>
+      <c r="H48" t="s">
+        <v>175</v>
+      </c>
+      <c r="I48">
+        <v>0.808445763919276</v>
+      </c>
+      <c r="J48" t="s">
+        <v>274</v>
+      </c>
+      <c r="K48">
+        <v>995</v>
+      </c>
+      <c r="L48">
+        <v>86</v>
+      </c>
+      <c r="M48">
+        <v>269</v>
+      </c>
+      <c r="N48" s="2" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14">
+      <c r="A49">
+        <v>48</v>
+      </c>
+      <c r="B49" t="s">
+        <v>61</v>
+      </c>
+      <c r="C49">
+        <v>22</v>
+      </c>
+      <c r="D49" t="b">
+        <v>1</v>
+      </c>
+      <c r="E49">
+        <v>0.1922450214147421</v>
+      </c>
+      <c r="F49" t="s">
+        <v>126</v>
+      </c>
+      <c r="G49" t="b">
+        <v>1</v>
+      </c>
+      <c r="H49" t="s">
+        <v>176</v>
+      </c>
+      <c r="I49">
+        <v>0.7905859018872378</v>
+      </c>
+      <c r="J49" t="s">
+        <v>275</v>
+      </c>
+      <c r="K49">
+        <v>179</v>
+      </c>
+      <c r="L49">
+        <v>29</v>
+      </c>
+      <c r="M49">
+        <v>6</v>
+      </c>
+      <c r="N49" s="2" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14">
+      <c r="A50">
+        <v>49</v>
+      </c>
+      <c r="B50" t="s">
+        <v>62</v>
+      </c>
+      <c r="C50">
+        <v>11</v>
+      </c>
+      <c r="D50" t="b">
+        <v>1</v>
+      </c>
+      <c r="E50">
+        <v>0.189471462639953</v>
+      </c>
+      <c r="F50" t="s">
+        <v>123</v>
+      </c>
+      <c r="G50" t="b">
+        <v>1</v>
+      </c>
+      <c r="H50" t="s">
+        <v>177</v>
+      </c>
+      <c r="I50">
+        <v>0.7876609195160683</v>
+      </c>
+      <c r="J50" t="s">
+        <v>276</v>
+      </c>
+      <c r="K50">
+        <v>36</v>
+      </c>
+      <c r="L50">
+        <v>4</v>
+      </c>
+      <c r="M50">
+        <v>2</v>
+      </c>
+      <c r="N50" s="2" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14">
+      <c r="A51">
+        <v>50</v>
+      </c>
+      <c r="B51" t="s">
+        <v>63</v>
+      </c>
+      <c r="C51">
+        <v>46</v>
+      </c>
+      <c r="D51" t="b">
+        <v>1</v>
+      </c>
+      <c r="E51">
+        <v>0.1740220062245915</v>
+      </c>
+      <c r="F51" t="s">
+        <v>121</v>
+      </c>
+      <c r="G51" t="b">
+        <v>1</v>
+      </c>
+      <c r="H51" t="s">
+        <v>178</v>
+      </c>
+      <c r="I51">
+        <v>0.7713679935936602</v>
+      </c>
+      <c r="J51" t="s">
+        <v>277</v>
+      </c>
+      <c r="K51">
+        <v>62</v>
+      </c>
+      <c r="L51">
+        <v>1</v>
+      </c>
+      <c r="M51">
+        <v>4</v>
+      </c>
+      <c r="N51" s="2" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14">
+      <c r="A52">
+        <v>51</v>
+      </c>
+      <c r="B52" t="s">
         <v>64</v>
       </c>
-      <c r="G40" t="b">
-        <v>1</v>
-      </c>
-      <c r="H40" t="s">
+      <c r="C52">
+        <v>6</v>
+      </c>
+      <c r="D52" t="b">
+        <v>1</v>
+      </c>
+      <c r="E52">
+        <v>0.1489326040222271</v>
+      </c>
+      <c r="F52" t="s">
+        <v>123</v>
+      </c>
+      <c r="G52" t="b">
+        <v>1</v>
+      </c>
+      <c r="H52" t="s">
+        <v>179</v>
+      </c>
+      <c r="I52">
+        <v>0.7449088250293748</v>
+      </c>
+      <c r="J52" t="s">
+        <v>278</v>
+      </c>
+      <c r="K52">
+        <v>381</v>
+      </c>
+      <c r="L52">
+        <v>48</v>
+      </c>
+      <c r="M52">
+        <v>75</v>
+      </c>
+      <c r="N52" s="2" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14">
+      <c r="A53">
+        <v>52</v>
+      </c>
+      <c r="B53" t="s">
+        <v>65</v>
+      </c>
+      <c r="C53">
+        <v>5</v>
+      </c>
+      <c r="D53" t="b">
+        <v>1</v>
+      </c>
+      <c r="E53">
+        <v>0.1423816710837987</v>
+      </c>
+      <c r="F53" t="s">
+        <v>123</v>
+      </c>
+      <c r="G53" t="b">
+        <v>1</v>
+      </c>
+      <c r="H53" t="s">
+        <v>180</v>
+      </c>
+      <c r="I53">
+        <v>0.7380002411789843</v>
+      </c>
+      <c r="J53" t="s">
+        <v>279</v>
+      </c>
+      <c r="K53">
+        <v>7</v>
+      </c>
+      <c r="L53">
+        <v>1</v>
+      </c>
+      <c r="M53">
+        <v>0</v>
+      </c>
+      <c r="N53" s="2" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14">
+      <c r="A54">
+        <v>53</v>
+      </c>
+      <c r="B54" t="s">
+        <v>66</v>
+      </c>
+      <c r="C54">
+        <v>9</v>
+      </c>
+      <c r="D54" t="b">
+        <v>0</v>
+      </c>
+      <c r="E54">
+        <v>0.3757406303703453</v>
+      </c>
+      <c r="F54" t="s">
+        <v>114</v>
+      </c>
+      <c r="G54" t="b">
+        <v>1</v>
+      </c>
+      <c r="H54" t="s">
+        <v>181</v>
+      </c>
+      <c r="I54">
+        <v>0.7340995300319904</v>
+      </c>
+      <c r="J54" t="s">
+        <v>280</v>
+      </c>
+      <c r="K54">
+        <v>243</v>
+      </c>
+      <c r="L54">
+        <v>8</v>
+      </c>
+      <c r="M54">
+        <v>49</v>
+      </c>
+      <c r="N54" s="2" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14">
+      <c r="A55">
+        <v>54</v>
+      </c>
+      <c r="B55" t="s">
+        <v>67</v>
+      </c>
+      <c r="C55">
+        <v>5</v>
+      </c>
+      <c r="D55" t="b">
+        <v>0</v>
+      </c>
+      <c r="E55">
+        <v>0.3726065345126772</v>
+      </c>
+      <c r="F55" t="s">
+        <v>119</v>
+      </c>
+      <c r="G55" t="b">
+        <v>1</v>
+      </c>
+      <c r="H55" t="s">
+        <v>182</v>
+      </c>
+      <c r="I55">
+        <v>0.7307943269057535</v>
+      </c>
+      <c r="J55" t="s">
+        <v>281</v>
+      </c>
+      <c r="K55">
+        <v>0</v>
+      </c>
+      <c r="L55">
+        <v>1</v>
+      </c>
+      <c r="M55">
+        <v>0</v>
+      </c>
+      <c r="N55" s="2" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14">
+      <c r="A56">
+        <v>55</v>
+      </c>
+      <c r="B56" t="s">
+        <v>68</v>
+      </c>
+      <c r="C56">
+        <v>5</v>
+      </c>
+      <c r="D56" t="b">
+        <v>0</v>
+      </c>
+      <c r="E56">
+        <v>0.3694755588394245</v>
+      </c>
+      <c r="F56" t="s">
+        <v>119</v>
+      </c>
+      <c r="G56" t="b">
+        <v>1</v>
+      </c>
+      <c r="H56" t="s">
+        <v>183</v>
+      </c>
+      <c r="I56">
+        <v>0.7274924143116999</v>
+      </c>
+      <c r="J56" t="s">
+        <v>282</v>
+      </c>
+      <c r="K56">
+        <v>0</v>
+      </c>
+      <c r="L56">
+        <v>1</v>
+      </c>
+      <c r="M56">
+        <v>0</v>
+      </c>
+      <c r="N56" s="2" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14">
+      <c r="A57">
+        <v>56</v>
+      </c>
+      <c r="B57" t="s">
+        <v>69</v>
+      </c>
+      <c r="C57">
+        <v>54</v>
+      </c>
+      <c r="D57" t="b">
+        <v>0</v>
+      </c>
+      <c r="E57">
+        <v>0.3665692485311893</v>
+      </c>
+      <c r="F57" t="s">
+        <v>114</v>
+      </c>
+      <c r="G57" t="b">
+        <v>1</v>
+      </c>
+      <c r="H57" t="s">
+        <v>184</v>
+      </c>
+      <c r="I57">
+        <v>0.7244274327818303</v>
+      </c>
+      <c r="J57" t="s">
+        <v>283</v>
+      </c>
+      <c r="K57">
+        <v>191</v>
+      </c>
+      <c r="L57">
+        <v>7</v>
+      </c>
+      <c r="M57">
+        <v>59</v>
+      </c>
+      <c r="N57" s="2" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14">
+      <c r="A58">
+        <v>57</v>
+      </c>
+      <c r="B58" t="s">
+        <v>70</v>
+      </c>
+      <c r="C58">
+        <v>7</v>
+      </c>
+      <c r="D58" t="b">
+        <v>0</v>
+      </c>
+      <c r="E58">
+        <v>0.351808582278388</v>
+      </c>
+      <c r="F58" t="s">
+        <v>119</v>
+      </c>
+      <c r="G58" t="b">
+        <v>1</v>
+      </c>
+      <c r="H58" t="s">
+        <v>185</v>
+      </c>
+      <c r="I58">
+        <v>0.7088609018077594</v>
+      </c>
+      <c r="J58" t="s">
+        <v>284</v>
+      </c>
+      <c r="K58">
+        <v>37</v>
+      </c>
+      <c r="L58">
+        <v>5</v>
+      </c>
+      <c r="M58">
+        <v>0</v>
+      </c>
+      <c r="N58" s="2" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14">
+      <c r="A59">
+        <v>58</v>
+      </c>
+      <c r="B59" t="s">
+        <v>71</v>
+      </c>
+      <c r="C59">
+        <v>5</v>
+      </c>
+      <c r="D59" t="b">
+        <v>0</v>
+      </c>
+      <c r="E59">
+        <v>0.320463341026548</v>
+      </c>
+      <c r="F59" t="s">
+        <v>122</v>
+      </c>
+      <c r="G59" t="b">
+        <v>1</v>
+      </c>
+      <c r="H59" t="s">
+        <v>186</v>
+      </c>
+      <c r="I59">
+        <v>0.675804354055798</v>
+      </c>
+      <c r="J59" t="s">
+        <v>285</v>
+      </c>
+      <c r="K59">
+        <v>66</v>
+      </c>
+      <c r="L59">
+        <v>2</v>
+      </c>
+      <c r="M59">
+        <v>4</v>
+      </c>
+      <c r="N59" s="2" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14">
+      <c r="A60">
+        <v>59</v>
+      </c>
+      <c r="B60" t="s">
+        <v>72</v>
+      </c>
+      <c r="C60">
+        <v>31</v>
+      </c>
+      <c r="D60" t="b">
+        <v>0</v>
+      </c>
+      <c r="E60">
+        <v>0.31967411925932</v>
+      </c>
+      <c r="F60" t="s">
+        <v>121</v>
+      </c>
+      <c r="G60" t="b">
+        <v>1</v>
+      </c>
+      <c r="H60" t="s">
+        <v>187</v>
+      </c>
+      <c r="I60">
+        <v>0.6749720443975105</v>
+      </c>
+      <c r="J60" t="s">
+        <v>286</v>
+      </c>
+      <c r="K60">
+        <v>822</v>
+      </c>
+      <c r="L60">
+        <v>525</v>
+      </c>
+      <c r="M60">
+        <v>353</v>
+      </c>
+      <c r="N60" s="2" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14">
+      <c r="A61">
+        <v>60</v>
+      </c>
+      <c r="B61" t="s">
+        <v>73</v>
+      </c>
+      <c r="C61">
+        <v>6</v>
+      </c>
+      <c r="D61" t="b">
+        <v>0</v>
+      </c>
+      <c r="E61">
+        <v>0.3176507350301913</v>
+      </c>
+      <c r="F61" t="s">
+        <v>122</v>
+      </c>
+      <c r="G61" t="b">
+        <v>1</v>
+      </c>
+      <c r="H61" t="s">
+        <v>188</v>
+      </c>
+      <c r="I61">
+        <v>0.6728381926637379</v>
+      </c>
+      <c r="J61" t="s">
+        <v>287</v>
+      </c>
+      <c r="K61">
+        <v>80</v>
+      </c>
+      <c r="L61">
+        <v>2</v>
+      </c>
+      <c r="M61">
+        <v>3</v>
+      </c>
+      <c r="N61" s="2" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="62" spans="1:14">
+      <c r="A62">
+        <v>61</v>
+      </c>
+      <c r="B62" t="s">
+        <v>74</v>
+      </c>
+      <c r="C62">
+        <v>5</v>
+      </c>
+      <c r="D62" t="b">
+        <v>0</v>
+      </c>
+      <c r="E62">
+        <v>0.2925603062380691</v>
+      </c>
+      <c r="F62" t="s">
+        <v>126</v>
+      </c>
+      <c r="G62" t="b">
+        <v>1</v>
+      </c>
+      <c r="H62" t="s">
+        <v>189</v>
+      </c>
+      <c r="I62">
+        <v>0.6463779414625994</v>
+      </c>
+      <c r="J62" t="s">
+        <v>288</v>
+      </c>
+      <c r="K62">
+        <v>261</v>
+      </c>
+      <c r="L62">
+        <v>42</v>
+      </c>
+      <c r="M62">
+        <v>20</v>
+      </c>
+      <c r="N62" s="2" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="63" spans="1:14">
+      <c r="A63">
+        <v>62</v>
+      </c>
+      <c r="B63" t="s">
+        <v>75</v>
+      </c>
+      <c r="C63">
+        <v>16</v>
+      </c>
+      <c r="D63" t="b">
+        <v>0</v>
+      </c>
+      <c r="E63">
+        <v>0.2924491055120446</v>
+      </c>
+      <c r="F63" t="s">
+        <v>119</v>
+      </c>
+      <c r="G63" t="b">
+        <v>1</v>
+      </c>
+      <c r="H63" t="s">
+        <v>190</v>
+      </c>
+      <c r="I63">
+        <v>0.6462606696866271</v>
+      </c>
+      <c r="J63" t="s">
+        <v>289</v>
+      </c>
+      <c r="K63">
+        <v>19</v>
+      </c>
+      <c r="L63">
+        <v>1</v>
+      </c>
+      <c r="M63">
+        <v>0</v>
+      </c>
+      <c r="N63" s="2" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="64" spans="1:14">
+      <c r="A64">
+        <v>63</v>
+      </c>
+      <c r="B64" t="s">
+        <v>76</v>
+      </c>
+      <c r="C64">
+        <v>5</v>
+      </c>
+      <c r="D64" t="b">
+        <v>0</v>
+      </c>
+      <c r="E64">
+        <v>0.2890260463824977</v>
+      </c>
+      <c r="F64" t="s">
+        <v>119</v>
+      </c>
+      <c r="G64" t="b">
+        <v>1</v>
+      </c>
+      <c r="H64" t="s">
+        <v>191</v>
+      </c>
+      <c r="I64">
+        <v>0.6426507272183423</v>
+      </c>
+      <c r="J64" t="s">
+        <v>290</v>
+      </c>
+      <c r="K64">
+        <v>773</v>
+      </c>
+      <c r="L64">
+        <v>195</v>
+      </c>
+      <c r="M64">
+        <v>94</v>
+      </c>
+      <c r="N64" s="2" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="65" spans="1:14">
+      <c r="A65">
+        <v>64</v>
+      </c>
+      <c r="B65" t="s">
+        <v>77</v>
+      </c>
+      <c r="C65">
+        <v>49</v>
+      </c>
+      <c r="D65" t="b">
+        <v>0</v>
+      </c>
+      <c r="E65">
+        <v>0.288790680077343</v>
+      </c>
+      <c r="F65" t="s">
+        <v>121</v>
+      </c>
+      <c r="G65" t="b">
+        <v>1</v>
+      </c>
+      <c r="H65" t="s">
+        <v>192</v>
+      </c>
+      <c r="I65">
+        <v>0.6424025109917375</v>
+      </c>
+      <c r="J65" t="s">
+        <v>291</v>
+      </c>
+      <c r="K65">
+        <v>45</v>
+      </c>
+      <c r="L65">
+        <v>3</v>
+      </c>
+      <c r="M65">
+        <v>3</v>
+      </c>
+      <c r="N65" s="2" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="66" spans="1:14">
+      <c r="A66">
+        <v>65</v>
+      </c>
+      <c r="B66" t="s">
+        <v>78</v>
+      </c>
+      <c r="C66">
+        <v>31</v>
+      </c>
+      <c r="D66" t="b">
+        <v>0</v>
+      </c>
+      <c r="E66">
+        <v>0.2809739886152102</v>
+      </c>
+      <c r="F66" t="s">
+        <v>121</v>
+      </c>
+      <c r="G66" t="b">
+        <v>1</v>
+      </c>
+      <c r="H66" t="s">
+        <v>193</v>
+      </c>
+      <c r="I66">
+        <v>0.6341590640039056</v>
+      </c>
+      <c r="J66" t="s">
+        <v>292</v>
+      </c>
+      <c r="K66">
+        <v>177</v>
+      </c>
+      <c r="L66">
+        <v>66</v>
+      </c>
+      <c r="M66">
+        <v>55</v>
+      </c>
+      <c r="N66" s="2" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="67" spans="1:14">
+      <c r="A67">
+        <v>66</v>
+      </c>
+      <c r="B67" t="s">
+        <v>79</v>
+      </c>
+      <c r="C67">
+        <v>16</v>
+      </c>
+      <c r="D67" t="b">
+        <v>0</v>
+      </c>
+      <c r="E67">
+        <v>0.2691518685165296</v>
+      </c>
+      <c r="F67" t="s">
+        <v>120</v>
+      </c>
+      <c r="G67" t="b">
+        <v>1</v>
+      </c>
+      <c r="H67" t="s">
+        <v>194</v>
+      </c>
+      <c r="I67">
+        <v>0.6216915103350208</v>
+      </c>
+      <c r="J67" t="s">
+        <v>293</v>
+      </c>
+      <c r="K67">
+        <v>86</v>
+      </c>
+      <c r="L67">
+        <v>7</v>
+      </c>
+      <c r="M67">
+        <v>13</v>
+      </c>
+      <c r="N67" s="2" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="68" spans="1:14">
+      <c r="A68">
+        <v>67</v>
+      </c>
+      <c r="B68" t="s">
+        <v>80</v>
+      </c>
+      <c r="C68">
+        <v>13</v>
+      </c>
+      <c r="D68" t="b">
+        <v>0</v>
+      </c>
+      <c r="E68">
+        <v>0.2687084018196203</v>
+      </c>
+      <c r="F68" t="s">
+        <v>117</v>
+      </c>
+      <c r="G68" t="b">
+        <v>1</v>
+      </c>
+      <c r="H68" t="s">
+        <v>195</v>
+      </c>
+      <c r="I68">
+        <v>0.6212238323891085</v>
+      </c>
+      <c r="J68" t="s">
+        <v>294</v>
+      </c>
+      <c r="K68">
+        <v>218</v>
+      </c>
+      <c r="L68">
+        <v>10</v>
+      </c>
+      <c r="M68">
+        <v>48</v>
+      </c>
+      <c r="N68" s="2" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="69" spans="1:14">
+      <c r="A69">
+        <v>68</v>
+      </c>
+      <c r="B69" t="s">
+        <v>81</v>
+      </c>
+      <c r="C69">
+        <v>29</v>
+      </c>
+      <c r="D69" t="b">
+        <v>0</v>
+      </c>
+      <c r="E69">
+        <v>0.2667106205001776</v>
+      </c>
+      <c r="F69" t="s">
+        <v>114</v>
+      </c>
+      <c r="G69" t="b">
+        <v>1</v>
+      </c>
+      <c r="H69" t="s">
+        <v>196</v>
+      </c>
+      <c r="I69">
+        <v>0.6191169813665388</v>
+      </c>
+      <c r="J69" t="s">
+        <v>295</v>
+      </c>
+      <c r="K69">
+        <v>49</v>
+      </c>
+      <c r="L69">
+        <v>4</v>
+      </c>
+      <c r="M69">
+        <v>2</v>
+      </c>
+      <c r="N69" s="2" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="70" spans="1:14">
+      <c r="A70">
+        <v>69</v>
+      </c>
+      <c r="B70" t="s">
+        <v>82</v>
+      </c>
+      <c r="C70">
+        <v>15</v>
+      </c>
+      <c r="D70" t="b">
+        <v>0</v>
+      </c>
+      <c r="E70">
+        <v>0.2624129686698187</v>
+      </c>
+      <c r="F70" t="s">
+        <v>116</v>
+      </c>
+      <c r="G70" t="b">
+        <v>1</v>
+      </c>
+      <c r="H70" t="s">
+        <v>197</v>
+      </c>
+      <c r="I70">
+        <v>0.6145846974447098</v>
+      </c>
+      <c r="J70" t="s">
+        <v>296</v>
+      </c>
+      <c r="K70">
+        <v>61</v>
+      </c>
+      <c r="L70">
+        <v>6</v>
+      </c>
+      <c r="M70">
+        <v>11</v>
+      </c>
+      <c r="N70" s="2" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="71" spans="1:14">
+      <c r="A71">
+        <v>70</v>
+      </c>
+      <c r="B71" t="s">
+        <v>83</v>
+      </c>
+      <c r="C71">
+        <v>48</v>
+      </c>
+      <c r="D71" t="b">
+        <v>0</v>
+      </c>
+      <c r="E71">
+        <v>0.2610200894357837</v>
+      </c>
+      <c r="F71" t="s">
+        <v>114</v>
+      </c>
+      <c r="G71" t="b">
+        <v>1</v>
+      </c>
+      <c r="H71" t="s">
+        <v>198</v>
+      </c>
+      <c r="I71">
+        <v>0.613115773388817</v>
+      </c>
+      <c r="J71" t="s">
+        <v>297</v>
+      </c>
+      <c r="K71">
+        <v>236</v>
+      </c>
+      <c r="L71">
+        <v>11</v>
+      </c>
+      <c r="M71">
+        <v>77</v>
+      </c>
+      <c r="N71" s="2" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="72" spans="1:14">
+      <c r="A72">
+        <v>71</v>
+      </c>
+      <c r="B72" t="s">
+        <v>84</v>
+      </c>
+      <c r="C72">
+        <v>6</v>
+      </c>
+      <c r="D72" t="b">
+        <v>0</v>
+      </c>
+      <c r="E72">
+        <v>0.2578196274345523</v>
+      </c>
+      <c r="F72" t="s">
+        <v>119</v>
+      </c>
+      <c r="G72" t="b">
+        <v>1</v>
+      </c>
+      <c r="H72" t="s">
+        <v>199</v>
+      </c>
+      <c r="I72">
+        <v>0.6097405808317703</v>
+      </c>
+      <c r="J72" t="s">
+        <v>298</v>
+      </c>
+      <c r="K72">
+        <v>32</v>
+      </c>
+      <c r="L72">
+        <v>0</v>
+      </c>
+      <c r="M72">
+        <v>3</v>
+      </c>
+      <c r="N72" s="2" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="73" spans="1:14">
+      <c r="A73">
+        <v>72</v>
+      </c>
+      <c r="B73" t="s">
+        <v>85</v>
+      </c>
+      <c r="C73">
+        <v>13</v>
+      </c>
+      <c r="D73" t="b">
+        <v>0</v>
+      </c>
+      <c r="E73">
+        <v>0.2546323353297525</v>
+      </c>
+      <c r="F73" t="s">
+        <v>121</v>
+      </c>
+      <c r="G73" t="b">
+        <v>1</v>
+      </c>
+      <c r="H73" t="s">
+        <v>200</v>
+      </c>
+      <c r="I73">
+        <v>0.6063792771871356</v>
+      </c>
+      <c r="J73" t="s">
+        <v>299</v>
+      </c>
+      <c r="K73">
+        <v>114</v>
+      </c>
+      <c r="L73">
+        <v>6</v>
+      </c>
+      <c r="M73">
+        <v>13</v>
+      </c>
+      <c r="N73" s="2" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="74" spans="1:14">
+      <c r="A74">
+        <v>73</v>
+      </c>
+      <c r="B74" t="s">
+        <v>86</v>
+      </c>
+      <c r="C74">
+        <v>45</v>
+      </c>
+      <c r="D74" t="b">
+        <v>0</v>
+      </c>
+      <c r="E74">
+        <v>0.252966713520381</v>
+      </c>
+      <c r="F74" t="s">
+        <v>115</v>
+      </c>
+      <c r="G74" t="b">
+        <v>1</v>
+      </c>
+      <c r="H74" t="s">
+        <v>201</v>
+      </c>
+      <c r="I74">
+        <v>0.6046227200614199</v>
+      </c>
+      <c r="J74" t="s">
+        <v>300</v>
+      </c>
+      <c r="K74">
+        <v>24</v>
+      </c>
+      <c r="L74">
+        <v>2</v>
+      </c>
+      <c r="M74">
+        <v>0</v>
+      </c>
+      <c r="N74" s="2" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="75" spans="1:14">
+      <c r="A75">
+        <v>74</v>
+      </c>
+      <c r="B75" t="s">
+        <v>87</v>
+      </c>
+      <c r="C75">
+        <v>37</v>
+      </c>
+      <c r="D75" t="b">
+        <v>0</v>
+      </c>
+      <c r="E75">
+        <v>0.2525994429756026</v>
+      </c>
+      <c r="F75" t="s">
+        <v>115</v>
+      </c>
+      <c r="G75" t="b">
+        <v>1</v>
+      </c>
+      <c r="H75" t="s">
+        <v>202</v>
+      </c>
+      <c r="I75">
+        <v>0.6042353982282964</v>
+      </c>
+      <c r="J75" t="s">
+        <v>301</v>
+      </c>
+      <c r="K75">
+        <v>21</v>
+      </c>
+      <c r="L75">
+        <v>0</v>
+      </c>
+      <c r="M75">
+        <v>1</v>
+      </c>
+      <c r="N75" s="2" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="76" spans="1:14">
+      <c r="A76">
+        <v>75</v>
+      </c>
+      <c r="B76" t="s">
+        <v>88</v>
+      </c>
+      <c r="C76">
+        <v>20</v>
+      </c>
+      <c r="D76" t="b">
+        <v>0</v>
+      </c>
+      <c r="E76">
+        <v>0.2356282656668251</v>
+      </c>
+      <c r="F76" t="s">
+        <v>115</v>
+      </c>
+      <c r="G76" t="b">
+        <v>1</v>
+      </c>
+      <c r="H76" t="s">
+        <v>203</v>
+      </c>
+      <c r="I76">
+        <v>0.5863376724265634</v>
+      </c>
+      <c r="J76" t="s">
+        <v>302</v>
+      </c>
+      <c r="K76">
+        <v>3</v>
+      </c>
+      <c r="L76">
+        <v>1</v>
+      </c>
+      <c r="M76">
+        <v>0</v>
+      </c>
+      <c r="N76" s="2" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="77" spans="1:14">
+      <c r="A77">
+        <v>76</v>
+      </c>
+      <c r="B77" t="s">
+        <v>89</v>
+      </c>
+      <c r="C77">
+        <v>17</v>
+      </c>
+      <c r="D77" t="b">
+        <v>0</v>
+      </c>
+      <c r="E77">
+        <v>0.2347396677474993</v>
+      </c>
+      <c r="F77" t="s">
+        <v>126</v>
+      </c>
+      <c r="G77" t="b">
+        <v>1</v>
+      </c>
+      <c r="H77" t="s">
+        <v>204</v>
+      </c>
+      <c r="I77">
+        <v>0.5854005611337683</v>
+      </c>
+      <c r="J77" t="s">
+        <v>303</v>
+      </c>
+      <c r="K77">
+        <v>85</v>
+      </c>
+      <c r="L77">
+        <v>7</v>
+      </c>
+      <c r="M77">
+        <v>9</v>
+      </c>
+      <c r="N77" s="2" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="78" spans="1:14">
+      <c r="A78">
+        <v>77</v>
+      </c>
+      <c r="B78" t="s">
+        <v>90</v>
+      </c>
+      <c r="C78">
+        <v>8</v>
+      </c>
+      <c r="D78" t="b">
+        <v>0</v>
+      </c>
+      <c r="E78">
+        <v>0.2336316792628552</v>
+      </c>
+      <c r="F78" t="s">
+        <v>121</v>
+      </c>
+      <c r="G78" t="b">
+        <v>1</v>
+      </c>
+      <c r="H78" t="s">
+        <v>205</v>
+      </c>
+      <c r="I78">
+        <v>0.5842320815563743</v>
+      </c>
+      <c r="J78" t="s">
+        <v>304</v>
+      </c>
+      <c r="K78">
+        <v>52</v>
+      </c>
+      <c r="L78">
+        <v>2</v>
+      </c>
+      <c r="M78">
+        <v>6</v>
+      </c>
+      <c r="N78" s="2" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="79" spans="1:14">
+      <c r="A79">
+        <v>78</v>
+      </c>
+      <c r="B79" t="s">
+        <v>91</v>
+      </c>
+      <c r="C79">
+        <v>15</v>
+      </c>
+      <c r="D79" t="b">
+        <v>0</v>
+      </c>
+      <c r="E79">
+        <v>0.2301983153966515</v>
+      </c>
+      <c r="F79" t="s">
+        <v>114</v>
+      </c>
+      <c r="G79" t="b">
+        <v>1</v>
+      </c>
+      <c r="H79" t="s">
+        <v>206</v>
+      </c>
+      <c r="I79">
+        <v>0.5806112717600433</v>
+      </c>
+      <c r="J79" t="s">
+        <v>305</v>
+      </c>
+      <c r="K79">
+        <v>260</v>
+      </c>
+      <c r="L79">
+        <v>8</v>
+      </c>
+      <c r="M79">
+        <v>51</v>
+      </c>
+      <c r="N79" s="2" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="80" spans="1:14">
+      <c r="A80">
+        <v>79</v>
+      </c>
+      <c r="B80" t="s">
+        <v>92</v>
+      </c>
+      <c r="C80">
+        <v>49</v>
+      </c>
+      <c r="D80" t="b">
+        <v>0</v>
+      </c>
+      <c r="E80">
+        <v>0.2225780098358209</v>
+      </c>
+      <c r="F80" t="s">
+        <v>122</v>
+      </c>
+      <c r="G80" t="b">
+        <v>1</v>
+      </c>
+      <c r="H80" t="s">
+        <v>207</v>
+      </c>
+      <c r="I80">
+        <v>0.5725749324435817</v>
+      </c>
+      <c r="J80" t="s">
+        <v>306</v>
+      </c>
+      <c r="K80">
+        <v>67</v>
+      </c>
+      <c r="L80">
+        <v>0</v>
+      </c>
+      <c r="M80">
+        <v>2</v>
+      </c>
+      <c r="N80" s="2" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="81" spans="1:14">
+      <c r="A81">
+        <v>80</v>
+      </c>
+      <c r="B81" t="s">
+        <v>93</v>
+      </c>
+      <c r="C81">
+        <v>54</v>
+      </c>
+      <c r="D81" t="b">
+        <v>0</v>
+      </c>
+      <c r="E81">
+        <v>0.2199829202553288</v>
+      </c>
+      <c r="F81" t="s">
+        <v>121</v>
+      </c>
+      <c r="G81" t="b">
+        <v>1</v>
+      </c>
+      <c r="H81" t="s">
+        <v>208</v>
+      </c>
+      <c r="I81">
+        <v>0.5698381628666969</v>
+      </c>
+      <c r="J81" t="s">
+        <v>307</v>
+      </c>
+      <c r="K81">
+        <v>58</v>
+      </c>
+      <c r="L81">
+        <v>10</v>
+      </c>
+      <c r="M81">
+        <v>12</v>
+      </c>
+      <c r="N81" s="2" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="82" spans="1:14">
+      <c r="A82">
+        <v>81</v>
+      </c>
+      <c r="B82" t="s">
+        <v>94</v>
+      </c>
+      <c r="C82">
+        <v>10</v>
+      </c>
+      <c r="D82" t="b">
+        <v>0</v>
+      </c>
+      <c r="E82">
+        <v>0.2151329885583641</v>
+      </c>
+      <c r="F82" t="s">
+        <v>121</v>
+      </c>
+      <c r="G82" t="b">
+        <v>1</v>
+      </c>
+      <c r="H82" t="s">
+        <v>209</v>
+      </c>
+      <c r="I82">
+        <v>0.5647234471289434</v>
+      </c>
+      <c r="J82" t="s">
+        <v>308</v>
+      </c>
+      <c r="K82">
+        <v>2</v>
+      </c>
+      <c r="L82">
+        <v>1</v>
+      </c>
+      <c r="M82">
+        <v>0</v>
+      </c>
+      <c r="N82" s="2" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="83" spans="1:14">
+      <c r="A83">
+        <v>82</v>
+      </c>
+      <c r="B83" t="s">
+        <v>95</v>
+      </c>
+      <c r="C83">
+        <v>31</v>
+      </c>
+      <c r="D83" t="b">
+        <v>0</v>
+      </c>
+      <c r="E83">
+        <v>0.2137950644113636</v>
+      </c>
+      <c r="F83" t="s">
+        <v>119</v>
+      </c>
+      <c r="G83" t="b">
+        <v>1</v>
+      </c>
+      <c r="H83" t="s">
+        <v>210</v>
+      </c>
+      <c r="I83">
+        <v>0.5633124784559481</v>
+      </c>
+      <c r="J83" t="s">
+        <v>309</v>
+      </c>
+      <c r="K83">
+        <v>71</v>
+      </c>
+      <c r="L83">
+        <v>2</v>
+      </c>
+      <c r="M83">
+        <v>8</v>
+      </c>
+      <c r="N83" s="2" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="84" spans="1:14">
+      <c r="A84">
+        <v>83</v>
+      </c>
+      <c r="B84" t="s">
+        <v>96</v>
+      </c>
+      <c r="C84">
+        <v>18</v>
+      </c>
+      <c r="D84" t="b">
+        <v>0</v>
+      </c>
+      <c r="E84">
+        <v>0.2110056082770768</v>
+      </c>
+      <c r="F84" t="s">
+        <v>127</v>
+      </c>
+      <c r="G84" t="b">
+        <v>1</v>
+      </c>
+      <c r="H84" t="s">
+        <v>211</v>
+      </c>
+      <c r="I84">
+        <v>0.5603707308023186</v>
+      </c>
+      <c r="J84" t="s">
+        <v>310</v>
+      </c>
+      <c r="K84">
+        <v>55</v>
+      </c>
+      <c r="L84">
+        <v>5</v>
+      </c>
+      <c r="M84">
+        <v>25</v>
+      </c>
+      <c r="N84" s="2" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="85" spans="1:14">
+      <c r="A85">
+        <v>84</v>
+      </c>
+      <c r="B85" t="s">
+        <v>97</v>
+      </c>
+      <c r="C85">
+        <v>23</v>
+      </c>
+      <c r="D85" t="b">
+        <v>0</v>
+      </c>
+      <c r="E85">
+        <v>0.2064226052386952</v>
+      </c>
+      <c r="F85" t="s">
+        <v>121</v>
+      </c>
+      <c r="G85" t="b">
+        <v>1</v>
+      </c>
+      <c r="H85" t="s">
+        <v>212</v>
+      </c>
+      <c r="I85">
+        <v>0.5555375168044282</v>
+      </c>
+      <c r="J85" t="s">
+        <v>311</v>
+      </c>
+      <c r="K85">
+        <v>480</v>
+      </c>
+      <c r="L85">
+        <v>9</v>
+      </c>
+      <c r="M85">
+        <v>164</v>
+      </c>
+      <c r="N85" s="2" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="86" spans="1:14">
+      <c r="A86">
+        <v>85</v>
+      </c>
+      <c r="B86" t="s">
+        <v>98</v>
+      </c>
+      <c r="C86">
+        <v>39</v>
+      </c>
+      <c r="D86" t="b">
+        <v>0</v>
+      </c>
+      <c r="E86">
+        <v>0.202535982763112</v>
+      </c>
+      <c r="F86" t="s">
+        <v>118</v>
+      </c>
+      <c r="G86" t="b">
+        <v>1</v>
+      </c>
+      <c r="H86" t="s">
+        <v>213</v>
+      </c>
+      <c r="I86">
+        <v>0.5514387025561753</v>
+      </c>
+      <c r="J86" t="s">
+        <v>312</v>
+      </c>
+      <c r="K86">
+        <v>459</v>
+      </c>
+      <c r="L86">
+        <v>20</v>
+      </c>
+      <c r="M86">
+        <v>148</v>
+      </c>
+      <c r="N86" s="2" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="87" spans="1:14">
+      <c r="A87">
+        <v>86</v>
+      </c>
+      <c r="B87" t="s">
+        <v>99</v>
+      </c>
+      <c r="C87">
+        <v>7</v>
+      </c>
+      <c r="D87" t="b">
+        <v>0</v>
+      </c>
+      <c r="E87">
+        <v>0.1954190729418908</v>
+      </c>
+      <c r="F87" t="s">
+        <v>128</v>
+      </c>
+      <c r="G87" t="b">
+        <v>1</v>
+      </c>
+      <c r="H87" t="s">
+        <v>214</v>
+      </c>
+      <c r="I87">
+        <v>0.5439332420793705</v>
+      </c>
+      <c r="J87" t="s">
+        <v>313</v>
+      </c>
+      <c r="K87">
+        <v>1</v>
+      </c>
+      <c r="L87">
+        <v>0</v>
+      </c>
+      <c r="M87">
+        <v>0</v>
+      </c>
+      <c r="N87" s="2" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="88" spans="1:14">
+      <c r="A88">
+        <v>87</v>
+      </c>
+      <c r="B88" t="s">
+        <v>100</v>
+      </c>
+      <c r="C88">
+        <v>9</v>
+      </c>
+      <c r="D88" t="b">
+        <v>0</v>
+      </c>
+      <c r="E88">
+        <v>0.1876105264472302</v>
+      </c>
+      <c r="F88" t="s">
+        <v>124</v>
+      </c>
+      <c r="G88" t="b">
+        <v>1</v>
+      </c>
+      <c r="H88" t="s">
+        <v>215</v>
+      </c>
+      <c r="I88">
+        <v>0.535698384736902</v>
+      </c>
+      <c r="J88" t="s">
+        <v>314</v>
+      </c>
+      <c r="K88">
+        <v>0</v>
+      </c>
+      <c r="L88">
+        <v>0</v>
+      </c>
+      <c r="M88">
+        <v>0</v>
+      </c>
+      <c r="N88" s="2" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="89" spans="1:14">
+      <c r="A89">
+        <v>88</v>
+      </c>
+      <c r="B89" t="s">
+        <v>101</v>
+      </c>
+      <c r="C89">
+        <v>24</v>
+      </c>
+      <c r="D89" t="b">
+        <v>0</v>
+      </c>
+      <c r="E89">
+        <v>0.1822343107039133</v>
+      </c>
+      <c r="F89" t="s">
+        <v>126</v>
+      </c>
+      <c r="G89" t="b">
+        <v>1</v>
+      </c>
+      <c r="H89" t="s">
+        <v>216</v>
+      </c>
+      <c r="I89">
+        <v>0.5300286522561105</v>
+      </c>
+      <c r="J89" t="s">
+        <v>315</v>
+      </c>
+      <c r="K89">
+        <v>53</v>
+      </c>
+      <c r="L89">
+        <v>7</v>
+      </c>
+      <c r="M89">
+        <v>6</v>
+      </c>
+      <c r="N89" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="90" spans="1:14">
+      <c r="A90">
+        <v>89</v>
+      </c>
+      <c r="B90" t="s">
+        <v>102</v>
+      </c>
+      <c r="C90">
+        <v>23</v>
+      </c>
+      <c r="D90" t="b">
+        <v>0</v>
+      </c>
+      <c r="E90">
+        <v>0.1778531428929873</v>
+      </c>
+      <c r="F90" t="s">
+        <v>126</v>
+      </c>
+      <c r="G90" t="b">
+        <v>1</v>
+      </c>
+      <c r="H90" t="s">
+        <v>217</v>
+      </c>
+      <c r="I90">
+        <v>0.5254082927639746</v>
+      </c>
+      <c r="J90" t="s">
+        <v>316</v>
+      </c>
+      <c r="K90">
+        <v>34</v>
+      </c>
+      <c r="L90">
+        <v>10</v>
+      </c>
+      <c r="M90">
+        <v>6</v>
+      </c>
+      <c r="N90" s="2" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="91" spans="1:14">
+      <c r="A91">
+        <v>90</v>
+      </c>
+      <c r="B91" t="s">
         <v>103</v>
       </c>
-      <c r="I40">
-        <v>0.5340601593871769</v>
-      </c>
-      <c r="J40" t="s">
-        <v>142</v>
-      </c>
-      <c r="K40">
+      <c r="C91">
+        <v>25</v>
+      </c>
+      <c r="D91" t="b">
+        <v>0</v>
+      </c>
+      <c r="E91">
+        <v>0.1772481186302497</v>
+      </c>
+      <c r="F91" t="s">
+        <v>126</v>
+      </c>
+      <c r="G91" t="b">
+        <v>1</v>
+      </c>
+      <c r="H91" t="s">
+        <v>218</v>
+      </c>
+      <c r="I91">
+        <v>0.5247702369496456</v>
+      </c>
+      <c r="J91" t="s">
+        <v>317</v>
+      </c>
+      <c r="K91">
+        <v>24</v>
+      </c>
+      <c r="L91">
+        <v>3</v>
+      </c>
+      <c r="M91">
+        <v>4</v>
+      </c>
+      <c r="N91" s="2" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="92" spans="1:14">
+      <c r="A92">
+        <v>91</v>
+      </c>
+      <c r="B92" t="s">
+        <v>104</v>
+      </c>
+      <c r="C92">
+        <v>6</v>
+      </c>
+      <c r="D92" t="b">
+        <v>0</v>
+      </c>
+      <c r="E92">
+        <v>0.1668309165744295</v>
+      </c>
+      <c r="F92" t="s">
+        <v>116</v>
+      </c>
+      <c r="G92" t="b">
+        <v>1</v>
+      </c>
+      <c r="H92" t="s">
+        <v>219</v>
+      </c>
+      <c r="I92">
+        <v>0.5137843034092605</v>
+      </c>
+      <c r="J92" t="s">
+        <v>318</v>
+      </c>
+      <c r="K92">
+        <v>78</v>
+      </c>
+      <c r="L92">
+        <v>6</v>
+      </c>
+      <c r="M92">
+        <v>1</v>
+      </c>
+      <c r="N92" s="2" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="93" spans="1:14">
+      <c r="A93">
+        <v>92</v>
+      </c>
+      <c r="B93" t="s">
+        <v>105</v>
+      </c>
+      <c r="C93">
+        <v>12</v>
+      </c>
+      <c r="D93" t="b">
+        <v>0</v>
+      </c>
+      <c r="E93">
+        <v>0.1661852395226628</v>
+      </c>
+      <c r="F93" t="s">
+        <v>126</v>
+      </c>
+      <c r="G93" t="b">
+        <v>1</v>
+      </c>
+      <c r="H93" t="s">
+        <v>220</v>
+      </c>
+      <c r="I93">
+        <v>0.5131033753499552</v>
+      </c>
+      <c r="J93" t="s">
+        <v>319</v>
+      </c>
+      <c r="K93">
+        <v>23</v>
+      </c>
+      <c r="L93">
+        <v>3</v>
+      </c>
+      <c r="M93">
+        <v>2</v>
+      </c>
+      <c r="N93" s="2" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="94" spans="1:14">
+      <c r="A94">
+        <v>93</v>
+      </c>
+      <c r="B94" t="s">
+        <v>106</v>
+      </c>
+      <c r="C94">
+        <v>9</v>
+      </c>
+      <c r="D94" t="b">
+        <v>0</v>
+      </c>
+      <c r="E94">
+        <v>0.1645078294498286</v>
+      </c>
+      <c r="F94" t="s">
+        <v>126</v>
+      </c>
+      <c r="G94" t="b">
+        <v>1</v>
+      </c>
+      <c r="H94" t="s">
+        <v>221</v>
+      </c>
+      <c r="I94">
+        <v>0.5113343863756238</v>
+      </c>
+      <c r="J94" t="s">
+        <v>320</v>
+      </c>
+      <c r="K94">
+        <v>173</v>
+      </c>
+      <c r="L94">
+        <v>35</v>
+      </c>
+      <c r="M94">
+        <v>24</v>
+      </c>
+      <c r="N94" s="2" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="95" spans="1:14">
+      <c r="A95">
+        <v>94</v>
+      </c>
+      <c r="B95" t="s">
+        <v>107</v>
+      </c>
+      <c r="C95">
+        <v>48</v>
+      </c>
+      <c r="D95" t="b">
+        <v>0</v>
+      </c>
+      <c r="E95">
+        <v>0.1590881722841045</v>
+      </c>
+      <c r="F95" t="s">
+        <v>114</v>
+      </c>
+      <c r="G95" t="b">
+        <v>1</v>
+      </c>
+      <c r="H95" t="s">
+        <v>222</v>
+      </c>
+      <c r="I95">
+        <v>0.5056188407698773</v>
+      </c>
+      <c r="J95" t="s">
+        <v>321</v>
+      </c>
+      <c r="K95">
+        <v>168</v>
+      </c>
+      <c r="L95">
+        <v>14</v>
+      </c>
+      <c r="M95">
+        <v>73</v>
+      </c>
+      <c r="N95" s="2" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="96" spans="1:14">
+      <c r="A96">
+        <v>95</v>
+      </c>
+      <c r="B96" t="s">
+        <v>108</v>
+      </c>
+      <c r="C96">
+        <v>51</v>
+      </c>
+      <c r="D96" t="b">
+        <v>0</v>
+      </c>
+      <c r="E96">
+        <v>0.1580210349468855</v>
+      </c>
+      <c r="F96" t="s">
+        <v>118</v>
+      </c>
+      <c r="G96" t="b">
+        <v>1</v>
+      </c>
+      <c r="H96" t="s">
+        <v>223</v>
+      </c>
+      <c r="I96">
+        <v>0.5044934426253149</v>
+      </c>
+      <c r="J96" t="s">
+        <v>322</v>
+      </c>
+      <c r="K96">
+        <v>1039</v>
+      </c>
+      <c r="L96">
+        <v>32</v>
+      </c>
+      <c r="M96">
+        <v>324</v>
+      </c>
+      <c r="N96" s="2" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="97" spans="1:14">
+      <c r="A97">
+        <v>96</v>
+      </c>
+      <c r="B97" t="s">
+        <v>109</v>
+      </c>
+      <c r="C97">
+        <v>18</v>
+      </c>
+      <c r="D97" t="b">
+        <v>0</v>
+      </c>
+      <c r="E97">
+        <v>0.1556090848416722</v>
+      </c>
+      <c r="F97" t="s">
+        <v>123</v>
+      </c>
+      <c r="G97" t="b">
+        <v>1</v>
+      </c>
+      <c r="H97" t="s">
+        <v>224</v>
+      </c>
+      <c r="I97">
+        <v>0.5019498110996315</v>
+      </c>
+      <c r="J97" t="s">
+        <v>323</v>
+      </c>
+      <c r="K97">
+        <v>71</v>
+      </c>
+      <c r="L97">
+        <v>6</v>
+      </c>
+      <c r="M97">
+        <v>0</v>
+      </c>
+      <c r="N97" s="2" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="98" spans="1:14">
+      <c r="A98">
+        <v>97</v>
+      </c>
+      <c r="B98" t="s">
+        <v>110</v>
+      </c>
+      <c r="C98">
+        <v>12</v>
+      </c>
+      <c r="D98" t="b">
+        <v>0</v>
+      </c>
+      <c r="E98">
+        <v>0.1524033779678499</v>
+      </c>
+      <c r="F98" t="s">
+        <v>116</v>
+      </c>
+      <c r="G98" t="b">
+        <v>1</v>
+      </c>
+      <c r="H98" t="s">
+        <v>225</v>
+      </c>
+      <c r="I98">
+        <v>0.4985690873239906</v>
+      </c>
+      <c r="J98" t="s">
+        <v>324</v>
+      </c>
+      <c r="K98">
+        <v>45</v>
+      </c>
+      <c r="L98">
+        <v>2</v>
+      </c>
+      <c r="M98">
+        <v>14</v>
+      </c>
+      <c r="N98" s="2" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="99" spans="1:14">
+      <c r="A99">
+        <v>98</v>
+      </c>
+      <c r="B99" t="s">
+        <v>111</v>
+      </c>
+      <c r="C99">
+        <v>8</v>
+      </c>
+      <c r="D99" t="b">
+        <v>0</v>
+      </c>
+      <c r="E99">
+        <v>0.1439768154432663</v>
+      </c>
+      <c r="F99" t="s">
+        <v>126</v>
+      </c>
+      <c r="G99" t="b">
+        <v>1</v>
+      </c>
+      <c r="H99" t="s">
+        <v>226</v>
+      </c>
+      <c r="I99">
+        <v>0.4896824731090677</v>
+      </c>
+      <c r="J99" t="s">
+        <v>325</v>
+      </c>
+      <c r="K99">
+        <v>2827</v>
+      </c>
+      <c r="L99">
+        <v>541</v>
+      </c>
+      <c r="M99">
+        <v>477</v>
+      </c>
+      <c r="N99" s="2" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="100" spans="1:14">
+      <c r="A100">
+        <v>99</v>
+      </c>
+      <c r="B100" t="s">
+        <v>112</v>
+      </c>
+      <c r="C100">
+        <v>6</v>
+      </c>
+      <c r="D100" t="b">
+        <v>0</v>
+      </c>
+      <c r="E100">
+        <v>0.1394795402581404</v>
+      </c>
+      <c r="F100" t="s">
+        <v>126</v>
+      </c>
+      <c r="G100" t="b">
+        <v>1</v>
+      </c>
+      <c r="H100" t="s">
+        <v>227</v>
+      </c>
+      <c r="I100">
+        <v>0.4849396673122836</v>
+      </c>
+      <c r="J100" t="s">
+        <v>326</v>
+      </c>
+      <c r="K100">
+        <v>23</v>
+      </c>
+      <c r="L100">
+        <v>1</v>
+      </c>
+      <c r="M100">
+        <v>4</v>
+      </c>
+      <c r="N100" s="2" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="101" spans="1:14">
+      <c r="A101">
         <v>100</v>
       </c>
-      <c r="L40">
-        <v>15</v>
-      </c>
-      <c r="M40">
-        <v>23</v>
-      </c>
-      <c r="N40" s="2" t="s">
-        <v>181</v>
+      <c r="B101" t="s">
+        <v>113</v>
+      </c>
+      <c r="C101">
+        <v>17</v>
+      </c>
+      <c r="D101" t="b">
+        <v>0</v>
+      </c>
+      <c r="E101">
+        <v>0.1394256372996809</v>
+      </c>
+      <c r="F101" t="s">
+        <v>125</v>
+      </c>
+      <c r="G101" t="b">
+        <v>1</v>
+      </c>
+      <c r="H101" t="s">
+        <v>228</v>
+      </c>
+      <c r="I101">
+        <v>0.4848828214993586</v>
+      </c>
+      <c r="J101" t="s">
+        <v>327</v>
+      </c>
+      <c r="K101">
+        <v>63</v>
+      </c>
+      <c r="L101">
+        <v>2</v>
+      </c>
+      <c r="M101">
+        <v>1</v>
+      </c>
+      <c r="N101" s="2" t="s">
+        <v>427</v>
       </c>
     </row>
   </sheetData>
@@ -2734,6 +6156,67 @@
     <hyperlink ref="N38" r:id="rId37"/>
     <hyperlink ref="N39" r:id="rId38"/>
     <hyperlink ref="N40" r:id="rId39"/>
+    <hyperlink ref="N41" r:id="rId40"/>
+    <hyperlink ref="N42" r:id="rId41"/>
+    <hyperlink ref="N43" r:id="rId42"/>
+    <hyperlink ref="N44" r:id="rId43"/>
+    <hyperlink ref="N45" r:id="rId44"/>
+    <hyperlink ref="N46" r:id="rId45"/>
+    <hyperlink ref="N47" r:id="rId46"/>
+    <hyperlink ref="N48" r:id="rId47"/>
+    <hyperlink ref="N49" r:id="rId48"/>
+    <hyperlink ref="N50" r:id="rId49"/>
+    <hyperlink ref="N51" r:id="rId50"/>
+    <hyperlink ref="N52" r:id="rId51"/>
+    <hyperlink ref="N53" r:id="rId52"/>
+    <hyperlink ref="N54" r:id="rId53"/>
+    <hyperlink ref="N55" r:id="rId54"/>
+    <hyperlink ref="N56" r:id="rId55"/>
+    <hyperlink ref="N57" r:id="rId56"/>
+    <hyperlink ref="N58" r:id="rId57"/>
+    <hyperlink ref="N59" r:id="rId58"/>
+    <hyperlink ref="N60" r:id="rId59"/>
+    <hyperlink ref="N61" r:id="rId60"/>
+    <hyperlink ref="N62" r:id="rId61"/>
+    <hyperlink ref="N63" r:id="rId62"/>
+    <hyperlink ref="N64" r:id="rId63"/>
+    <hyperlink ref="N65" r:id="rId64"/>
+    <hyperlink ref="N66" r:id="rId65"/>
+    <hyperlink ref="N67" r:id="rId66"/>
+    <hyperlink ref="N68" r:id="rId67"/>
+    <hyperlink ref="N69" r:id="rId68"/>
+    <hyperlink ref="N70" r:id="rId69"/>
+    <hyperlink ref="N71" r:id="rId70"/>
+    <hyperlink ref="N72" r:id="rId71"/>
+    <hyperlink ref="N73" r:id="rId72"/>
+    <hyperlink ref="N74" r:id="rId73"/>
+    <hyperlink ref="N75" r:id="rId74"/>
+    <hyperlink ref="N76" r:id="rId75"/>
+    <hyperlink ref="N77" r:id="rId76"/>
+    <hyperlink ref="N78" r:id="rId77"/>
+    <hyperlink ref="N79" r:id="rId78"/>
+    <hyperlink ref="N80" r:id="rId79"/>
+    <hyperlink ref="N81" r:id="rId80"/>
+    <hyperlink ref="N82" r:id="rId81"/>
+    <hyperlink ref="N83" r:id="rId82"/>
+    <hyperlink ref="N84" r:id="rId83"/>
+    <hyperlink ref="N85" r:id="rId84"/>
+    <hyperlink ref="N86" r:id="rId85"/>
+    <hyperlink ref="N87" r:id="rId86"/>
+    <hyperlink ref="N88" r:id="rId87"/>
+    <hyperlink ref="N89" r:id="rId88"/>
+    <hyperlink ref="N90" r:id="rId89"/>
+    <hyperlink ref="N91" r:id="rId90"/>
+    <hyperlink ref="N92" r:id="rId91"/>
+    <hyperlink ref="N93" r:id="rId92"/>
+    <hyperlink ref="N94" r:id="rId93"/>
+    <hyperlink ref="N95" r:id="rId94"/>
+    <hyperlink ref="N96" r:id="rId95"/>
+    <hyperlink ref="N97" r:id="rId96"/>
+    <hyperlink ref="N98" r:id="rId97"/>
+    <hyperlink ref="N99" r:id="rId98"/>
+    <hyperlink ref="N100" r:id="rId99"/>
+    <hyperlink ref="N101" r:id="rId100"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
